--- a/LineClass/found_levels.xlsx
+++ b/LineClass/found_levels.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UMD\AI\as-ai\LineClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7549E63C-0188-4AD0-A4B0-B60A8DF2594B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C241C9A-D178-4FE7-99DF-FB8C0ACD8F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="42315" windowHeight="17505" xr2:uid="{601CA898-2047-4D8A-9A99-963F279FF439}"/>
+    <workbookView xWindow="615" yWindow="1425" windowWidth="50130" windowHeight="17505" xr2:uid="{E743DC57-3E0B-40B1-BC6B-EF7851EBEC40}"/>
   </bookViews>
   <sheets>
     <sheet name="found_levels" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">found_levels!$A$1:$R$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">found_levels!$A$1:$R$90</definedName>
   </definedNames>
   <calcPr calcId="0" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="114">
   <si>
     <t>idx</t>
   </si>
@@ -79,172 +79,175 @@
     <t>Note</t>
   </si>
   <si>
-    <t>f25f ~3F4G</t>
+    <t>f5d6s~1F2F</t>
   </si>
   <si>
     <t>o</t>
   </si>
   <si>
+    <t>f5d6s</t>
+  </si>
+  <si>
+    <t>firm</t>
+  </si>
+  <si>
+    <t>this is the position IDEN2 already holds for this row, as 059003.000646</t>
+  </si>
+  <si>
+    <t>f5d2 ~3P4D</t>
+  </si>
+  <si>
+    <t>f5d2</t>
+  </si>
+  <si>
+    <t>f5d2 ~3P2F</t>
+  </si>
+  <si>
+    <t>weak</t>
+  </si>
+  <si>
+    <t>f5d6s~1D2D</t>
+  </si>
+  <si>
+    <t>f5d2 ~3P2D</t>
+  </si>
+  <si>
+    <t>this is the position IDEN2 already holds for this row, as 059003.000647</t>
+  </si>
+  <si>
+    <t>f27p ~3F4G</t>
+  </si>
+  <si>
+    <t>f27p</t>
+  </si>
+  <si>
+    <t>f5d6s~3D4D</t>
+  </si>
+  <si>
+    <t>f27d _3H4G</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f27d</t>
+  </si>
+  <si>
+    <t>f27d _3H4I</t>
+  </si>
+  <si>
+    <t>this is the position IDEN2 already holds for this row, as 059003.000648</t>
+  </si>
+  <si>
+    <t>f5d2 ~3F2D</t>
+  </si>
+  <si>
+    <t>f27d _3H4K</t>
+  </si>
+  <si>
+    <t>this is the position IDEN2 already holds for this row, as 059003.000649</t>
+  </si>
+  <si>
+    <t>f27p ~3F2G</t>
+  </si>
+  <si>
+    <t>f5d2 ~3P4F</t>
+  </si>
+  <si>
+    <t>f28s _3H4H</t>
+  </si>
+  <si>
+    <t>f28s</t>
+  </si>
+  <si>
+    <t>fd6p _1H2I</t>
+  </si>
+  <si>
+    <t>fd6p</t>
+  </si>
+  <si>
+    <t>f5d6s~3H4H</t>
+  </si>
+  <si>
+    <t>f27d _3H2I</t>
+  </si>
+  <si>
+    <t>f28s _3F2F</t>
+  </si>
+  <si>
+    <t>no support</t>
+  </si>
+  <si>
+    <t>f27p ~3F4F</t>
+  </si>
+  <si>
+    <t>5d3  _4F4F</t>
+  </si>
+  <si>
+    <t>5d3</t>
+  </si>
+  <si>
+    <t>fd6p _1G2H</t>
+  </si>
+  <si>
+    <t>this is the position IDEN2 already holds for this row, as 059003.000650</t>
+  </si>
+  <si>
+    <t>f27d _3H2G</t>
+  </si>
+  <si>
+    <t>f27d _3H4H</t>
+  </si>
+  <si>
+    <t>duplicate with row 518 (J 2.5), 0.000 cm^-1 away; duplicate with the position IDEN2 holds for row 518 (J 2.5), as 059003.000652, 0.002 cm^-1 away</t>
+  </si>
+  <si>
+    <t>f26d _3F2F</t>
+  </si>
+  <si>
+    <t>f26d</t>
+  </si>
+  <si>
+    <t>f25f ~1G2D</t>
+  </si>
+  <si>
     <t>f25f</t>
   </si>
   <si>
-    <t>firm</t>
-  </si>
-  <si>
-    <t>f5d6s~3D4D</t>
-  </si>
-  <si>
-    <t>f5d6s</t>
-  </si>
-  <si>
-    <t>this is the position IDEN2 already holds for this row, which has no level_id yet: it is marked in IDEN2 but is not a level of the pipeline</t>
-  </si>
-  <si>
-    <t>duplicate with row 915 (J 1.5), 0.080 cm^-1 away; this is the position IDEN2 already holds for this row, which has no level_id yet: it is marked in IDEN2 but is not a level of the pipeline</t>
-  </si>
-  <si>
-    <t>f5d6s~1F2F</t>
-  </si>
-  <si>
-    <t>f5d2 ~3P4D</t>
-  </si>
-  <si>
-    <t>f5d2</t>
-  </si>
-  <si>
-    <t>f27p ~3H2G</t>
-  </si>
-  <si>
-    <t>f27p</t>
-  </si>
-  <si>
-    <t>f27p ~3H4H</t>
-  </si>
-  <si>
-    <t>f5d2 ~3P2F</t>
-  </si>
-  <si>
-    <t>weak</t>
-  </si>
-  <si>
-    <t>f27p ~3F4G</t>
-  </si>
-  <si>
-    <t>f5d6s~1D2D</t>
-  </si>
-  <si>
-    <t>f5d2 ~3P2D</t>
-  </si>
-  <si>
-    <t>f27d _3H4H</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>f27d</t>
-  </si>
-  <si>
-    <t>f5d2 ~3P2G</t>
-  </si>
-  <si>
-    <t>f27d _3H4G</t>
-  </si>
-  <si>
-    <t>f27d _3H4I</t>
-  </si>
-  <si>
-    <t>f5d2 ~3F2D</t>
-  </si>
-  <si>
-    <t>f27d _3H4K</t>
-  </si>
-  <si>
-    <t>f5d2 ~3P4F</t>
-  </si>
-  <si>
-    <t>f27p ~3F2G</t>
-  </si>
-  <si>
-    <t>f28s _3H4H</t>
-  </si>
-  <si>
-    <t>f28s</t>
-  </si>
-  <si>
-    <t>f26d _3F2G</t>
-  </si>
-  <si>
-    <t>f26d</t>
-  </si>
-  <si>
-    <t>f5d6s~3H4H</t>
-  </si>
-  <si>
-    <t>f27d _3H2I</t>
-  </si>
-  <si>
-    <t>duplicate with row 447 (J 6.5), 0.000 cm^-1 away; duplicate with row 446 (J 7.5), 0.000 cm^-1 away</t>
-  </si>
-  <si>
-    <t>fd6p _1H2I</t>
-  </si>
-  <si>
-    <t>fd6p</t>
-  </si>
-  <si>
-    <t>5d3  _4F4F</t>
-  </si>
-  <si>
-    <t>5d3</t>
-  </si>
-  <si>
-    <t>fd6p _1G2H</t>
-  </si>
-  <si>
-    <t>duplicate with row 518 (J 2.5), 0.000 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f27d _3H2G</t>
-  </si>
-  <si>
-    <t>f27p ~3F4F</t>
-  </si>
-  <si>
-    <t>f25f ~1G2D</t>
-  </si>
-  <si>
     <t>f5d2 ~1G2D</t>
   </si>
   <si>
-    <t>duplicate with row 316 (J 3.5), 0.002 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f26d _3F2F</t>
-  </si>
-  <si>
-    <t>duplicate with row 1007 (J 1.5), 0.040 cm^-1 away; duplicate with the position IDEN2 holds for row 1007 (J 1.5), which has no level_id yet: it is marked in IDEN2 but is not a level of the pipeline, 0.042 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f5d2 ~1D2D</t>
-  </si>
-  <si>
-    <t>duplicate with row 1010 (J 2.5), 0.040 cm^-1 away; this is the position IDEN2 already holds for this row, which has no level_id yet: it is marked in IDEN2 but is not a level of the pipeline</t>
-  </si>
-  <si>
-    <t>duplicate with the position IDEN2 holds for row 525 (J 4.5), as 059003.000572, 0.015 cm^-1 away</t>
+    <t>duplicate with row 316 (J 3.5), 0.024 cm^-1 away</t>
+  </si>
+  <si>
+    <t>this is the position IDEN2 already holds for this row, as 059003.000651</t>
   </si>
   <si>
     <t>f5d6s~3F4F</t>
   </si>
   <si>
-    <t>f28s _3F2F</t>
-  </si>
-  <si>
-    <t>f26p ~3P2P</t>
-  </si>
-  <si>
-    <t>f26p</t>
+    <t>duplicate with row 446 (J 7.5), 0.000 cm^-1 away</t>
+  </si>
+  <si>
+    <t>f27d _3H2F</t>
+  </si>
+  <si>
+    <t>duplicate with row 392 (J 3.5), 0.000 cm^-1 away</t>
+  </si>
+  <si>
+    <t>f26d _3F4G</t>
+  </si>
+  <si>
+    <t>f27d _3F2H</t>
+  </si>
+  <si>
+    <t>duplicate with row 317 (J 4.5), 0.000 cm^-1 away; duplicate with row 321 (J 3.5), 0.020 cm^-1 away</t>
+  </si>
+  <si>
+    <t>f27d _3F4G</t>
+  </si>
+  <si>
+    <t>duplicate with row 447 (J 6.5), 0.000 cm^-1 away</t>
   </si>
   <si>
     <t>fd6p _1H2H</t>
@@ -253,133 +256,112 @@
     <t>fd6p _3H4I</t>
   </si>
   <si>
+    <t>f27d _3H4F</t>
+  </si>
+  <si>
+    <t>duplicate with row 406 (J 4.5), 0.000 cm^-1 away</t>
+  </si>
+  <si>
     <t>fd6p _1H2G</t>
   </si>
   <si>
-    <t>duplicate with row 315 (J 3.5), 0.002 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f27d _3H4F</t>
-  </si>
-  <si>
-    <t>duplicate with row 439 (J 6.5), 0.000 cm^-1 away; duplicate with row 446 (J 7.5), 0.000 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f27d _3H2F</t>
+    <t>duplicate with row 315 (J 3.5), 0.024 cm^-1 away</t>
+  </si>
+  <si>
+    <t>duplicate with row 421 (J 4.5), 0.000 cm^-1 away</t>
+  </si>
+  <si>
+    <t>duplicate with row 389 (J 3.5), 0.000 cm^-1 away</t>
+  </si>
+  <si>
+    <t>f26d _1G2F</t>
+  </si>
+  <si>
+    <t>f26f ~3H2G</t>
+  </si>
+  <si>
+    <t>f26f</t>
+  </si>
+  <si>
+    <t>f25g _3H4H</t>
+  </si>
+  <si>
+    <t>f25g</t>
+  </si>
+  <si>
+    <t>duplicate with the position IDEN2 holds for row 337 (J 3.5), as 059003.000600, 0.005 cm^-1 away</t>
+  </si>
+  <si>
+    <t>duplicate with row 521 (J 3.5), 0.000 cm^-1 away; this is the position IDEN2 already holds for this row, as 059003.000652</t>
+  </si>
+  <si>
+    <t>f28s _1G2G</t>
+  </si>
+  <si>
+    <t>f27d _3H2K</t>
+  </si>
+  <si>
+    <t>f27p ~1G2H</t>
   </si>
   <si>
     <t>f28s _3F4F</t>
   </si>
   <si>
-    <t>f25f ~1I2F</t>
-  </si>
-  <si>
-    <t>f26d _1G2F</t>
-  </si>
-  <si>
-    <t>f26f ~3H2G</t>
-  </si>
-  <si>
-    <t>f26f</t>
-  </si>
-  <si>
-    <t>f25g _3H4H</t>
-  </si>
-  <si>
-    <t>f25g</t>
-  </si>
-  <si>
-    <t>duplicate with the position IDEN2 holds for row 337 (J 3.5), as 059003.000600, 0.011 cm^-1 away</t>
-  </si>
-  <si>
-    <t>duplicate with row 521 (J 3.5), 0.000 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f27d _3F2H</t>
-  </si>
-  <si>
-    <t>duplicate with row 321 (J 3.5), 0.020 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f27d _3F4G</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>f28s _1G2G</t>
-  </si>
-  <si>
-    <t>f27p ~1G2H</t>
-  </si>
-  <si>
     <t>f25f ~3F4P</t>
   </si>
   <si>
-    <t>duplicate with row 439 (J 6.5), 0.000 cm^-1 away; duplicate with row 447 (J 6.5), 0.000 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f26p ~3P4P</t>
-  </si>
-  <si>
     <t>f27p ~3F4D</t>
   </si>
   <si>
     <t>fd6p _3G2H</t>
   </si>
   <si>
-    <t>duplicate with row 914 (J 2.5), 0.080 cm^-1 away; duplicate with the position IDEN2 holds for row 914 (J 2.5), which has no level_id yet: it is marked in IDEN2 but is not a level of the pipeline, 0.064 cm^-1 away</t>
+    <t>f27d _3F2G</t>
+  </si>
+  <si>
+    <t>duplicate with row 319 (J 5.5), 0.000 cm^-1 away; duplicate with row 321 (J 3.5), 0.020 cm^-1 away</t>
+  </si>
+  <si>
+    <t>f5d2 ~3F4P</t>
+  </si>
+  <si>
+    <t>this is the position IDEN2 already holds for this row, as 059003.000653</t>
+  </si>
+  <si>
+    <t>f26d _3F2D</t>
+  </si>
+  <si>
+    <t>f26d _1G2H</t>
+  </si>
+  <si>
+    <t>f27d _3F2F</t>
+  </si>
+  <si>
+    <t>f27d _3F4D</t>
+  </si>
+  <si>
+    <t>duplicate with row 319 (J 5.5), 0.020 cm^-1 away; duplicate with row 317 (J 4.5), 0.020 cm^-1 away</t>
   </si>
   <si>
     <t>f5d6s~3D2D</t>
   </si>
   <si>
-    <t>f5d2 ~3F4P</t>
-  </si>
-  <si>
-    <t>f26d _1G2H</t>
-  </si>
-  <si>
-    <t>no support</t>
-  </si>
-  <si>
-    <t>f26d _3F2D</t>
-  </si>
-  <si>
-    <t>f26d _3F4G</t>
-  </si>
-  <si>
-    <t>f27d _3F2F</t>
-  </si>
-  <si>
-    <t>f26s _3P4P</t>
-  </si>
-  <si>
-    <t>f26s</t>
-  </si>
-  <si>
-    <t>f27d _3F4D</t>
-  </si>
-  <si>
-    <t>duplicate with row 319 (J 5.5), 0.020 cm^-1 away</t>
+    <t>f27d _1G2H</t>
+  </si>
+  <si>
+    <t>f27d _3F4H</t>
+  </si>
+  <si>
+    <t>f25g _3F4F</t>
   </si>
   <si>
     <t>f25f ~3P4G</t>
   </si>
   <si>
-    <t>f27d _1G2H</t>
-  </si>
-  <si>
-    <t>duplicate with the position IDEN2 holds for row 332 (J 1.5), as 059003.000604, 0.010 cm^-1 away</t>
-  </si>
-  <si>
-    <t>f27d _3H2K</t>
+    <t>f25g _3F4G</t>
   </si>
   <si>
     <t>f25g _3F4I</t>
-  </si>
-  <si>
-    <t>f25g _3F4G</t>
   </si>
   <si>
     <t>f25g _3F2I</t>
@@ -525,7 +507,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -705,18 +687,6 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -878,10 +848,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1256,9 +1224,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE5B977-2EE7-4A64-B665-59414AEBC9CA}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:R107"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE7B52F-37E9-4757-BFB2-50AE26839FFD}">
+  <dimension ref="A1:R90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -1278,7 +1245,7 @@
     <col min="15" max="15" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="187.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="130.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1337,177 +1304,156 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>742</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>906</v>
+      </c>
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>2.5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2">
-        <v>116406.7</v>
-      </c>
-      <c r="G2" s="2">
-        <v>103.6</v>
-      </c>
-      <c r="H2" s="2">
-        <v>116617.16899999999</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="F2">
+        <v>94239.8</v>
+      </c>
+      <c r="G2">
+        <v>215.8</v>
+      </c>
+      <c r="H2">
+        <v>94876.468999999997</v>
+      </c>
+      <c r="I2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2">
-        <v>2</v>
-      </c>
-      <c r="K2" s="2">
-        <v>8.3520000000000003</v>
-      </c>
-      <c r="L2" s="2">
-        <v>20</v>
-      </c>
-      <c r="M2" s="2">
-        <v>9</v>
-      </c>
-      <c r="N2" s="2">
-        <v>210.46899999999999</v>
-      </c>
-      <c r="O2" s="2">
-        <v>294</v>
-      </c>
-      <c r="P2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>913</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>8.15</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2">
+        <v>8</v>
+      </c>
+      <c r="N2">
+        <v>636.66899999999998</v>
+      </c>
+      <c r="O2">
+        <v>217</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="D3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>986</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>1.5</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="1">
-        <v>92210.7</v>
-      </c>
-      <c r="G3" s="1">
-        <v>177.3</v>
-      </c>
-      <c r="H3" s="1">
-        <v>92091.770999999993</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>75159.899999999994</v>
+      </c>
+      <c r="G3">
+        <v>210.4</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>138</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="K3" s="1">
-        <v>7.0350000000000001</v>
-      </c>
-      <c r="L3" s="1">
-        <v>12</v>
-      </c>
-      <c r="M3" s="1">
-        <v>7</v>
-      </c>
-      <c r="N3" s="1">
-        <v>-118.929</v>
-      </c>
-      <c r="O3" s="1">
-        <v>210</v>
-      </c>
-      <c r="P3" s="1" t="b">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>951</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>2.5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>83140.800000000003</v>
+      </c>
+      <c r="G4">
+        <v>210.4</v>
+      </c>
+      <c r="H4">
+        <v>82633.520999999993</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
-      <c r="Q3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>914</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1">
-        <v>91642.6</v>
-      </c>
-      <c r="G4" s="1">
-        <v>177.3</v>
-      </c>
-      <c r="H4" s="1">
-        <v>91197.850999999995</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>16.917000000000002</v>
-      </c>
-      <c r="L4" s="1">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>11</v>
-      </c>
-      <c r="N4" s="1">
-        <v>-444.74900000000002</v>
-      </c>
-      <c r="O4" s="1">
-        <v>209</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="N4">
+        <v>-507.279</v>
+      </c>
+      <c r="O4">
+        <v>172</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>2.5</v>
@@ -1516,33 +1462,51 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>94239.8</v>
+        <v>88538.4</v>
       </c>
       <c r="G5">
-        <v>177.3</v>
+        <v>215.8</v>
+      </c>
+      <c r="H5">
+        <v>87829.748999999996</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>12.101000000000001</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>7</v>
+      </c>
+      <c r="N5">
+        <v>-708.65099999999995</v>
       </c>
       <c r="O5">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>1.5</v>
@@ -1551,240 +1515,234 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>75159.899999999994</v>
+        <v>72363.600000000006</v>
       </c>
       <c r="G6">
-        <v>212.7</v>
+        <v>210.4</v>
+      </c>
+      <c r="H6">
+        <v>71767.221000000005</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>9.4339999999999993</v>
+      </c>
+      <c r="L6">
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>-596.37900000000002</v>
       </c>
       <c r="O6">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>691</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>4.5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>118596.3</v>
+      </c>
+      <c r="G7">
+        <v>42.3</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>332</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>719</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1">
-        <v>117665.3</v>
-      </c>
-      <c r="G7" s="1">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="H7" s="1">
-        <v>117712.65</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>12.212999999999999</v>
-      </c>
-      <c r="L7" s="1">
-        <v>11</v>
-      </c>
-      <c r="M7" s="1">
-        <v>5</v>
-      </c>
-      <c r="N7" s="1">
-        <v>47.35</v>
-      </c>
-      <c r="O7" s="1">
-        <v>314</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>90172.3</v>
+        <v>90091.7</v>
       </c>
       <c r="G8">
-        <v>177.3</v>
+        <v>215.8</v>
       </c>
       <c r="H8">
-        <v>90481.350999999995</v>
+        <v>90050.028999999995</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8">
-        <v>7.492</v>
+        <v>2.6</v>
       </c>
       <c r="L8">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>309.05099999999999</v>
+        <v>-41.670999999999999</v>
       </c>
       <c r="O8">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
-      </c>
-      <c r="R8" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>747</v>
+        <v>513</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>116010</v>
+        <v>130272.1</v>
       </c>
       <c r="G9">
-        <v>32.200000000000003</v>
+        <v>91.5</v>
       </c>
       <c r="H9">
-        <v>116074.99</v>
+        <v>130096.086</v>
       </c>
       <c r="I9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>28.864000000000001</v>
+        <v>3.5009999999999999</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>64.989999999999995</v>
+        <v>-176.01400000000001</v>
       </c>
       <c r="O9">
-        <v>289</v>
+        <v>2205</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
-      </c>
-      <c r="R9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>951</v>
+        <v>499</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C10">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F10">
-        <v>83140.800000000003</v>
+        <v>131826.4</v>
       </c>
       <c r="G10">
-        <v>212.7</v>
+        <v>91.5</v>
       </c>
       <c r="H10">
-        <v>82633.509000000005</v>
+        <v>131665.06599999999</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>0.97199999999999998</v>
+        <v>4.4109999999999996</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-507.291</v>
+        <v>-161.334</v>
       </c>
       <c r="O10">
-        <v>172</v>
+        <v>2216</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -1792,34 +1750,37 @@
       <c r="Q10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>691</v>
+        <v>994</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>118596.3</v>
+        <v>73369.899999999994</v>
       </c>
       <c r="G11">
-        <v>32.200000000000003</v>
+        <v>210.4</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="O11">
-        <v>332</v>
+        <v>130</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -1828,33 +1789,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>924</v>
+        <v>491</v>
       </c>
       <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="C12">
-        <v>2.5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
       <c r="F12">
-        <v>88538.4</v>
+        <v>132226.20000000001</v>
       </c>
       <c r="G12">
-        <v>177.3</v>
+        <v>91.5</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="O12">
-        <v>199</v>
+        <v>2224</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -1865,146 +1826,128 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>998</v>
+        <v>522</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>72363.600000000006</v>
+        <v>129628.2</v>
       </c>
       <c r="G13">
-        <v>212.7</v>
+        <v>91.5</v>
       </c>
       <c r="H13">
-        <v>71767.229000000007</v>
+        <v>129498.086</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>10.576000000000001</v>
+        <v>8.484</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>-596.37099999999998</v>
+        <v>-130.114</v>
       </c>
       <c r="O13">
-        <v>126</v>
+        <v>2197</v>
       </c>
       <c r="P13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>496</v>
+        <v>705</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C14">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>131987.20000000001</v>
+        <v>118086.9</v>
       </c>
       <c r="G14">
-        <v>87.9</v>
-      </c>
-      <c r="H14">
-        <v>131910.54699999999</v>
-      </c>
-      <c r="I14" t="s">
-        <v>21</v>
+        <v>42.3</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>324</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
         <v>1</v>
-      </c>
-      <c r="K14">
-        <v>6.9059999999999997</v>
-      </c>
-      <c r="L14">
-        <v>6</v>
-      </c>
-      <c r="M14">
-        <v>5</v>
-      </c>
-      <c r="N14">
-        <v>-76.653000000000006</v>
-      </c>
-      <c r="O14">
-        <v>2219</v>
-      </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>497</v>
+        <v>987</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>131895.4</v>
+        <v>74670.600000000006</v>
       </c>
       <c r="G15">
-        <v>87.9</v>
+        <v>210.4</v>
       </c>
       <c r="H15">
-        <v>131776.40700000001</v>
+        <v>74456.620999999999</v>
       </c>
       <c r="I15" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>7.1239999999999997</v>
+        <v>1.57</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -2013,80 +1956,59 @@
         <v>4</v>
       </c>
       <c r="N15">
-        <v>-118.99299999999999</v>
+        <v>-213.97900000000001</v>
       </c>
       <c r="O15">
-        <v>2218</v>
+        <v>137</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
-      </c>
-      <c r="R15" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>919</v>
+        <v>501</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C16">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F16">
-        <v>90091.7</v>
+        <v>131319.4</v>
       </c>
       <c r="G16">
-        <v>177.3</v>
-      </c>
-      <c r="H16">
-        <v>90050.031000000003</v>
-      </c>
-      <c r="I16" t="s">
-        <v>33</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>2214</v>
+      </c>
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
         <v>1</v>
-      </c>
-      <c r="K16">
-        <v>2.117</v>
-      </c>
-      <c r="L16">
-        <v>9</v>
-      </c>
-      <c r="M16">
-        <v>5</v>
-      </c>
-      <c r="N16">
-        <v>-41.668999999999997</v>
-      </c>
-      <c r="O16">
-        <v>204</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>955</v>
+        <v>675</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2095,90 +2017,72 @@
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>82034.3</v>
+        <v>119248.3</v>
       </c>
       <c r="G17">
-        <v>212.7</v>
-      </c>
-      <c r="H17">
-        <v>82084.069000000003</v>
-      </c>
-      <c r="I17" t="s">
-        <v>21</v>
+        <v>42.3</v>
       </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>340</v>
+      </c>
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
         <v>1</v>
-      </c>
-      <c r="K17">
-        <v>6.5039999999999996</v>
-      </c>
-      <c r="L17">
-        <v>11</v>
-      </c>
-      <c r="M17">
-        <v>5</v>
-      </c>
-      <c r="N17">
-        <v>49.768999999999998</v>
-      </c>
-      <c r="O17">
-        <v>168</v>
-      </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>513</v>
+        <v>442</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C18">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F18">
-        <v>130272.1</v>
+        <v>134118.1</v>
       </c>
       <c r="G18">
-        <v>87.9</v>
+        <v>404.2</v>
       </c>
       <c r="H18">
-        <v>130096.087</v>
+        <v>133790.144</v>
       </c>
       <c r="I18" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>5.351</v>
+        <v>2.5630000000000002</v>
       </c>
       <c r="L18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N18">
-        <v>-176.01300000000001</v>
+        <v>-327.95600000000002</v>
       </c>
       <c r="O18">
-        <v>2205</v>
+        <v>2238</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -2189,172 +2093,190 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>499</v>
+        <v>932</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C19">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>131826.4</v>
+        <v>86015.9</v>
       </c>
       <c r="G19">
-        <v>87.9</v>
-      </c>
-      <c r="H19">
-        <v>131665.06700000001</v>
-      </c>
-      <c r="I19" t="s">
-        <v>21</v>
+        <v>215.8</v>
       </c>
       <c r="J19">
-        <v>2</v>
-      </c>
-      <c r="K19">
-        <v>4.2960000000000003</v>
-      </c>
-      <c r="L19">
-        <v>5</v>
-      </c>
-      <c r="M19">
-        <v>5</v>
-      </c>
-      <c r="N19">
-        <v>-161.333</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>2216</v>
+        <v>191</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
       </c>
       <c r="Q19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>994</v>
+        <v>439</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C20">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F20">
-        <v>73369.899999999994</v>
+        <v>134204.5</v>
       </c>
       <c r="G20">
-        <v>212.7</v>
+        <v>91.5</v>
+      </c>
+      <c r="H20">
+        <v>134061.18599999999</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>1.9390000000000001</v>
+      </c>
+      <c r="L20">
+        <v>6</v>
+      </c>
+      <c r="M20">
+        <v>3</v>
+      </c>
+      <c r="N20">
+        <v>-143.31399999999999</v>
       </c>
       <c r="O20">
-        <v>130</v>
+        <v>2241</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>372</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21">
+        <v>3.5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21">
+        <v>136082.5</v>
+      </c>
+      <c r="G21">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="H21">
+        <v>136251.15100000001</v>
+      </c>
+      <c r="I21" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>491</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21">
-        <v>4.5</v>
-      </c>
-      <c r="D21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21">
-        <v>132226.20000000001</v>
-      </c>
-      <c r="G21">
-        <v>87.9</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
+      <c r="K21">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L21">
+        <v>4</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>168.65100000000001</v>
       </c>
       <c r="O21">
-        <v>2224</v>
+        <v>2281</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>522</v>
+        <v>710</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C22">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F22">
-        <v>129628.2</v>
+        <v>117972.7</v>
       </c>
       <c r="G22">
-        <v>87.9</v>
+        <v>42.3</v>
       </c>
       <c r="H22">
-        <v>129498.087</v>
+        <v>117947.711</v>
       </c>
       <c r="I22" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>8.093</v>
+        <v>0.106</v>
       </c>
       <c r="L22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N22">
-        <v>-130.113</v>
+        <v>-24.989000000000001</v>
       </c>
       <c r="O22">
-        <v>2197</v>
+        <v>320</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
@@ -2365,189 +2287,231 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>987</v>
+        <v>375</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <v>2.5</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="F23">
-        <v>74670.600000000006</v>
+        <v>135976.6</v>
       </c>
       <c r="G23">
-        <v>212.7</v>
-      </c>
-      <c r="H23">
-        <v>74456.629000000001</v>
-      </c>
-      <c r="I23" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>2279</v>
+      </c>
+      <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
         <v>1</v>
       </c>
-      <c r="K23">
-        <v>0.41</v>
-      </c>
-      <c r="L23">
-        <v>10</v>
-      </c>
-      <c r="M23">
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>672</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24">
+        <v>5.5</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24">
+        <v>119339.6</v>
+      </c>
+      <c r="G24">
+        <v>404.2</v>
+      </c>
+      <c r="H24">
+        <v>119552.40399999999</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>11.125999999999999</v>
+      </c>
+      <c r="L24">
+        <v>7</v>
+      </c>
+      <c r="M24">
+        <v>6</v>
+      </c>
+      <c r="N24">
+        <v>212.804</v>
+      </c>
+      <c r="O24">
+        <v>2085</v>
+      </c>
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>488</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25">
+        <v>3.5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25">
+        <v>132460.5</v>
+      </c>
+      <c r="G25">
+        <v>91.5</v>
+      </c>
+      <c r="H25">
+        <v>132507.606</v>
+      </c>
+      <c r="I25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>2.1349999999999998</v>
+      </c>
+      <c r="L25">
         <v>4</v>
       </c>
-      <c r="N23">
-        <v>-213.971</v>
-      </c>
-      <c r="O23">
-        <v>137</v>
-      </c>
-      <c r="P23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>705</v>
-      </c>
-      <c r="B24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24">
+      <c r="M25">
+        <v>4</v>
+      </c>
+      <c r="N25">
+        <v>47.106000000000002</v>
+      </c>
+      <c r="O25">
+        <v>2226</v>
+      </c>
+      <c r="P25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>521</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26">
         <v>3.5</v>
       </c>
-      <c r="D24" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24">
-        <v>118086.9</v>
-      </c>
-      <c r="G24">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>324</v>
-      </c>
-      <c r="P24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>501</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25">
-        <v>5.5</v>
-      </c>
-      <c r="D25" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25">
-        <v>131319.4</v>
-      </c>
-      <c r="G25">
-        <v>74.5</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>2214</v>
-      </c>
-      <c r="P25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>675</v>
-      </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26">
-        <v>4.5</v>
-      </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F26">
-        <v>119248.3</v>
+        <v>129738.7</v>
       </c>
       <c r="G26">
-        <v>32.200000000000003</v>
+        <v>91.5</v>
+      </c>
+      <c r="H26">
+        <v>129877.14599999999</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="K26">
+        <v>5.6580000000000004</v>
+      </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26">
+        <v>138.446</v>
       </c>
       <c r="O26">
-        <v>340</v>
+        <v>2198</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
       </c>
       <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C27">
         <v>3.5</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F27">
-        <v>108099.1</v>
+        <v>108201.7</v>
       </c>
       <c r="G27">
-        <v>61</v>
+        <v>60.4</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="O27">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -2558,299 +2522,299 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>932</v>
+        <v>632</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C28">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D28" t="s">
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F28">
-        <v>86015.9</v>
+        <v>121757.4</v>
       </c>
       <c r="G28">
-        <v>177.3</v>
-      </c>
-      <c r="H28">
-        <v>86011.990999999995</v>
-      </c>
-      <c r="I28" t="s">
-        <v>33</v>
+        <v>106.1</v>
       </c>
       <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>361</v>
+      </c>
+      <c r="P28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
         <v>1</v>
-      </c>
-      <c r="K28">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="L28">
-        <v>7</v>
-      </c>
-      <c r="M28">
-        <v>4</v>
-      </c>
-      <c r="N28">
-        <v>-3.9089999999999998</v>
-      </c>
-      <c r="O28">
-        <v>191</v>
-      </c>
-      <c r="P28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>439</v>
+        <v>944</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C29">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F29">
-        <v>134204.5</v>
+        <v>84315.7</v>
       </c>
       <c r="G29">
-        <v>87.9</v>
+        <v>210.4</v>
       </c>
       <c r="H29">
-        <v>134004.06700000001</v>
+        <v>84588.600999999995</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K29">
-        <v>1.6930000000000001</v>
+        <v>17.791</v>
       </c>
       <c r="L29">
+        <v>8</v>
+      </c>
+      <c r="M29">
         <v>7</v>
       </c>
-      <c r="M29">
-        <v>3</v>
-      </c>
       <c r="N29">
-        <v>-200.43299999999999</v>
+        <v>272.90100000000001</v>
       </c>
       <c r="O29">
-        <v>2241</v>
+        <v>179</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
-      </c>
-      <c r="R29" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>442</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C30">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F30">
-        <v>134118.1</v>
+        <v>137284.29999999999</v>
       </c>
       <c r="G30">
-        <v>404.2</v>
+        <v>134</v>
       </c>
       <c r="H30">
-        <v>134104.875</v>
+        <v>137068.18799999999</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>4.4039999999999999</v>
+        <v>1.085</v>
       </c>
       <c r="L30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>-13.225</v>
+        <v>-216.11199999999999</v>
       </c>
       <c r="O30">
-        <v>2238</v>
+        <v>2321</v>
       </c>
       <c r="P30" t="b">
         <v>0</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
+      </c>
+      <c r="R30" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>666</v>
+        <v>449</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C31">
         <v>5.5</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F31">
-        <v>119778.7</v>
+        <v>133993</v>
       </c>
       <c r="G31">
-        <v>32.200000000000003</v>
+        <v>404.2</v>
       </c>
       <c r="H31">
-        <v>119809.29</v>
+        <v>133745.96400000001</v>
       </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>11.884</v>
+        <v>1.95</v>
       </c>
       <c r="L31">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M31">
         <v>4</v>
       </c>
       <c r="N31">
-        <v>30.59</v>
+        <v>-247.036</v>
       </c>
       <c r="O31">
-        <v>344</v>
+        <v>2234</v>
       </c>
       <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>432</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32">
+        <v>5.5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32">
+        <v>134353.1</v>
+      </c>
+      <c r="G32">
+        <v>91.5</v>
+      </c>
+      <c r="H32">
+        <v>134249.12599999999</v>
+      </c>
+      <c r="I32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32">
         <v>1</v>
       </c>
-      <c r="Q31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>375</v>
-      </c>
-      <c r="B32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32">
-        <v>2.5</v>
-      </c>
-      <c r="D32" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32">
-        <v>135976.6</v>
-      </c>
-      <c r="G32">
-        <v>132.1</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
+      <c r="K32">
+        <v>1.3560000000000001</v>
+      </c>
+      <c r="L32">
+        <v>4</v>
+      </c>
+      <c r="M32">
+        <v>4</v>
+      </c>
+      <c r="N32">
+        <v>-103.974</v>
       </c>
       <c r="O32">
-        <v>2279</v>
+        <v>2242</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
       </c>
       <c r="Q32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>672</v>
+        <v>1010</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C33">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F33">
-        <v>119339.6</v>
+        <v>70304.2</v>
       </c>
       <c r="G33">
-        <v>404.2</v>
+        <v>210.4</v>
       </c>
       <c r="H33">
-        <v>119552.395</v>
+        <v>70490.600999999995</v>
       </c>
       <c r="I33" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J33">
+        <v>2</v>
+      </c>
+      <c r="K33">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="L33">
+        <v>4</v>
+      </c>
+      <c r="M33">
         <v>3</v>
       </c>
-      <c r="K33">
-        <v>10.976000000000001</v>
-      </c>
-      <c r="L33">
-        <v>8</v>
-      </c>
-      <c r="M33">
-        <v>6</v>
-      </c>
       <c r="N33">
-        <v>212.79499999999999</v>
+        <v>186.40100000000001</v>
       </c>
       <c r="O33">
-        <v>2085</v>
+        <v>114</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
@@ -2861,49 +2825,49 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>129738.7</v>
+        <v>129564</v>
       </c>
       <c r="G34">
-        <v>87.9</v>
+        <v>91.5</v>
       </c>
       <c r="H34">
-        <v>129877.147</v>
+        <v>129454.486</v>
       </c>
       <c r="I34" t="s">
         <v>21</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>5.1959999999999997</v>
+        <v>12.888999999999999</v>
       </c>
       <c r="L34">
         <v>5</v>
       </c>
       <c r="M34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>138.447</v>
+        <v>-109.514</v>
       </c>
       <c r="O34">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="P34" t="b">
         <v>0</v>
@@ -2912,54 +2876,54 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>488</v>
+        <v>937</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C35">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F35">
-        <v>132460.5</v>
+        <v>84871.5</v>
       </c>
       <c r="G35">
-        <v>87.9</v>
+        <v>215.8</v>
       </c>
       <c r="H35">
-        <v>132390.68700000001</v>
+        <v>84914.828999999998</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35">
-        <v>2.2509999999999999</v>
+        <v>6.8230000000000004</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>-69.813000000000002</v>
+        <v>43.329000000000001</v>
       </c>
       <c r="O35">
-        <v>2226</v>
+        <v>186</v>
       </c>
       <c r="P35" t="b">
         <v>0</v>
@@ -2970,137 +2934,161 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>661</v>
+        <v>447</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C36">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F36">
-        <v>119970.6</v>
+        <v>134001.60000000001</v>
       </c>
       <c r="G36">
-        <v>32.200000000000003</v>
+        <v>91.5</v>
       </c>
       <c r="H36">
-        <v>119998.51</v>
+        <v>133945.386</v>
       </c>
       <c r="I36" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>11.712</v>
+        <v>8.8019999999999996</v>
       </c>
       <c r="L36">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>27.91</v>
+        <v>-56.213999999999999</v>
       </c>
       <c r="O36">
-        <v>347</v>
+        <v>2235</v>
       </c>
       <c r="P36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>632</v>
+        <v>389</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C37">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F37">
-        <v>121757.4</v>
+        <v>135213.6</v>
       </c>
       <c r="G37">
-        <v>103.6</v>
+        <v>91.5</v>
+      </c>
+      <c r="H37">
+        <v>135414.24600000001</v>
+      </c>
+      <c r="I37" t="s">
+        <v>26</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K37">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+      <c r="M37">
+        <v>2</v>
+      </c>
+      <c r="N37">
+        <v>200.64599999999999</v>
       </c>
       <c r="O37">
-        <v>361</v>
+        <v>2273</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
       </c>
       <c r="Q37" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R37" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>944</v>
+        <v>856</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C38">
         <v>2.5</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F38">
-        <v>84315.7</v>
+        <v>105790.1</v>
       </c>
       <c r="G38">
-        <v>212.7</v>
+        <v>60.4</v>
       </c>
       <c r="H38">
-        <v>84588.589000000007</v>
+        <v>105721.304</v>
       </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J38">
         <v>3</v>
       </c>
       <c r="K38">
-        <v>17.004999999999999</v>
+        <v>2.9169999999999998</v>
       </c>
       <c r="L38">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>272.88900000000001</v>
+        <v>-68.796000000000006</v>
       </c>
       <c r="O38">
-        <v>179</v>
+        <v>2013</v>
       </c>
       <c r="P38" t="b">
         <v>0</v>
@@ -3111,49 +3099,49 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C39">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="F39">
-        <v>137284.29999999999</v>
+        <v>136995</v>
       </c>
       <c r="G39">
-        <v>132.1</v>
+        <v>91.5</v>
       </c>
       <c r="H39">
-        <v>137068.17300000001</v>
+        <v>136902.68599999999</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J39">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>1.6779999999999999</v>
+        <v>11.345000000000001</v>
       </c>
       <c r="L39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-216.12700000000001</v>
+        <v>-92.313999999999993</v>
       </c>
       <c r="O39">
-        <v>2321</v>
+        <v>2317</v>
       </c>
       <c r="P39" t="b">
         <v>0</v>
@@ -3162,89 +3150,107 @@
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>825</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C40">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F40">
-        <v>108201.7</v>
+        <v>136692.4</v>
       </c>
       <c r="G40">
-        <v>61</v>
+        <v>91.5</v>
+      </c>
+      <c r="H40">
+        <v>136779.766</v>
+      </c>
+      <c r="I40" t="s">
+        <v>26</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="K40">
+        <v>2.1819999999999999</v>
+      </c>
+      <c r="L40">
+        <v>4</v>
+      </c>
+      <c r="M40">
+        <v>2</v>
+      </c>
+      <c r="N40">
+        <v>87.366</v>
       </c>
       <c r="O40">
-        <v>2043</v>
+        <v>2309</v>
       </c>
       <c r="P40" t="b">
         <v>0</v>
       </c>
       <c r="Q40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>1010</v>
+        <v>446</v>
       </c>
       <c r="B41" t="s">
         <v>36</v>
       </c>
       <c r="C41">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F41">
-        <v>70304.2</v>
+        <v>134002</v>
       </c>
       <c r="G41">
-        <v>212.7</v>
+        <v>91.5</v>
       </c>
       <c r="H41">
-        <v>70477.748999999996</v>
+        <v>133945.386</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J41">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K41">
-        <v>4.319</v>
+        <v>13.537000000000001</v>
       </c>
       <c r="L41">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41">
-        <v>173.54900000000001</v>
+        <v>-56.613999999999997</v>
       </c>
       <c r="O41">
-        <v>114</v>
+        <v>2236</v>
       </c>
       <c r="P41" t="b">
         <v>0</v>
@@ -3253,54 +3259,54 @@
         <v>0</v>
       </c>
       <c r="R41" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>449</v>
+        <v>500</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C42">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F42">
-        <v>133993</v>
+        <v>131498.1</v>
       </c>
       <c r="G42">
         <v>404.2</v>
       </c>
       <c r="H42">
-        <v>133745.95499999999</v>
+        <v>130461.204</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J42">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>3.806</v>
+        <v>6.7919999999999998</v>
       </c>
       <c r="L42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M42">
         <v>4</v>
       </c>
       <c r="N42">
-        <v>-247.04499999999999</v>
+        <v>-1036.896</v>
       </c>
       <c r="O42">
-        <v>2234</v>
+        <v>2215</v>
       </c>
       <c r="P42" t="b">
         <v>0</v>
@@ -3309,74 +3315,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>710</v>
+        <v>670</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C43">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D43" t="s">
         <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F43">
-        <v>117972.7</v>
+        <v>119376.3</v>
       </c>
       <c r="G43">
-        <v>32.200000000000003</v>
+        <v>42.3</v>
+      </c>
+      <c r="H43">
+        <v>119299.431</v>
+      </c>
+      <c r="I43" t="s">
+        <v>26</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L43">
+        <v>5</v>
+      </c>
+      <c r="M43">
+        <v>2</v>
+      </c>
+      <c r="N43">
+        <v>-76.869</v>
       </c>
       <c r="O43">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="P43" t="b">
         <v>0</v>
       </c>
       <c r="Q43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>1007</v>
+        <v>711</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C44">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F44">
-        <v>70577.899999999994</v>
+        <v>117932.1</v>
       </c>
       <c r="G44">
-        <v>212.7</v>
+        <v>404.2</v>
       </c>
       <c r="H44">
-        <v>70477.789000000004</v>
+        <v>117889.024</v>
       </c>
       <c r="I44" t="s">
         <v>21</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44">
-        <v>25.263999999999999</v>
+        <v>17.867000000000001</v>
       </c>
       <c r="L44">
         <v>9</v>
@@ -3385,228 +3409,231 @@
         <v>7</v>
       </c>
       <c r="N44">
-        <v>-100.111</v>
+        <v>-43.076000000000001</v>
       </c>
       <c r="O44">
-        <v>117</v>
+        <v>2068</v>
       </c>
       <c r="P44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
-      </c>
-      <c r="R44" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>523</v>
+        <v>421</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="C45">
         <v>4.5</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F45">
-        <v>129564</v>
+        <v>134464</v>
       </c>
       <c r="G45">
-        <v>87.9</v>
+        <v>91.5</v>
       </c>
       <c r="H45">
-        <v>129454.48699999999</v>
+        <v>134696.62599999999</v>
       </c>
       <c r="I45" t="s">
         <v>21</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>11.695</v>
+        <v>4.9660000000000002</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M45">
         <v>5</v>
       </c>
       <c r="N45">
-        <v>-109.51300000000001</v>
+        <v>232.626</v>
       </c>
       <c r="O45">
-        <v>2196</v>
+        <v>2251</v>
       </c>
       <c r="P45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
       <c r="R45" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>937</v>
+        <v>316</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C46">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E46" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F46">
-        <v>84871.5</v>
+        <v>137240.9</v>
       </c>
       <c r="G46">
-        <v>177.3</v>
+        <v>404.2</v>
       </c>
       <c r="H46">
-        <v>84914.831000000006</v>
+        <v>137068.16399999999</v>
       </c>
       <c r="I46" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K46">
-        <v>8.7940000000000005</v>
+        <v>3.246</v>
       </c>
       <c r="L46">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>43.331000000000003</v>
+        <v>-172.73599999999999</v>
       </c>
       <c r="O46">
-        <v>186</v>
+        <v>2320</v>
       </c>
       <c r="P46" t="b">
         <v>0</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
+      </c>
+      <c r="R46" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C47">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E47" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F47">
-        <v>134353.1</v>
+        <v>134714.79999999999</v>
       </c>
       <c r="G47">
-        <v>87.9</v>
+        <v>91.5</v>
       </c>
       <c r="H47">
-        <v>134503.40700000001</v>
+        <v>134696.62599999999</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K47">
-        <v>1.9119999999999999</v>
+        <v>11.978</v>
       </c>
       <c r="L47">
         <v>5</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>150.30699999999999</v>
+        <v>-18.173999999999999</v>
       </c>
       <c r="O47">
-        <v>2242</v>
+        <v>2263</v>
       </c>
       <c r="P47" t="b">
         <v>0</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
+      </c>
+      <c r="R47" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>372</v>
+        <v>492</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C48">
         <v>3.5</v>
       </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E48" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F48">
-        <v>136082.5</v>
+        <v>132136</v>
       </c>
       <c r="G48">
-        <v>74.5</v>
+        <v>91.5</v>
       </c>
       <c r="H48">
-        <v>135946.217</v>
+        <v>131830.84599999999</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J48">
         <v>2</v>
       </c>
       <c r="K48">
-        <v>1.71</v>
+        <v>2.3210000000000002</v>
       </c>
       <c r="L48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M48">
         <v>3</v>
       </c>
       <c r="N48">
-        <v>-136.28299999999999</v>
+        <v>-305.154</v>
       </c>
       <c r="O48">
-        <v>2281</v>
+        <v>2223</v>
       </c>
       <c r="P48" t="b">
         <v>0</v>
@@ -3617,125 +3644,128 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>940</v>
+        <v>834</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="C49">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49">
+        <v>107743.5</v>
+      </c>
+      <c r="G49">
+        <v>60.4</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>2035</v>
+      </c>
+      <c r="P49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>392</v>
+      </c>
+      <c r="B50" t="s">
         <v>73</v>
-      </c>
-      <c r="F49">
-        <v>84630.8</v>
-      </c>
-      <c r="G49">
-        <v>112.5</v>
-      </c>
-      <c r="H49">
-        <v>84592.032000000007</v>
-      </c>
-      <c r="I49" t="s">
-        <v>21</v>
-      </c>
-      <c r="J49">
-        <v>12</v>
-      </c>
-      <c r="K49">
-        <v>24.122</v>
-      </c>
-      <c r="L49">
-        <v>8</v>
-      </c>
-      <c r="M49">
-        <v>7</v>
-      </c>
-      <c r="N49">
-        <v>-38.768000000000001</v>
-      </c>
-      <c r="O49">
-        <v>183</v>
-      </c>
-      <c r="P49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>670</v>
-      </c>
-      <c r="B50" t="s">
-        <v>61</v>
       </c>
       <c r="C50">
         <v>3.5</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F50">
-        <v>119376.3</v>
+        <v>135131.5</v>
       </c>
       <c r="G50">
-        <v>32.200000000000003</v>
+        <v>91.5</v>
+      </c>
+      <c r="H50">
+        <v>135414.24600000001</v>
+      </c>
+      <c r="I50" t="s">
+        <v>26</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L50">
+        <v>3</v>
+      </c>
+      <c r="M50">
+        <v>2</v>
+      </c>
+      <c r="N50">
+        <v>282.74599999999998</v>
       </c>
       <c r="O50">
-        <v>343</v>
+        <v>2271</v>
       </c>
       <c r="P50" t="b">
         <v>0</v>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R50" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>500</v>
+        <v>799</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C51">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F51">
-        <v>131498.1</v>
+        <v>111465.9</v>
       </c>
       <c r="G51">
-        <v>404.2</v>
+        <v>60.4</v>
       </c>
       <c r="H51">
-        <v>130461.215</v>
+        <v>111600.54399999999</v>
       </c>
       <c r="I51" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J51">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>4.516</v>
+        <v>7.97</v>
       </c>
       <c r="L51">
         <v>6</v>
@@ -3744,10 +3774,10 @@
         <v>3</v>
       </c>
       <c r="N51">
-        <v>-1036.885</v>
+        <v>134.64400000000001</v>
       </c>
       <c r="O51">
-        <v>2215</v>
+        <v>2058</v>
       </c>
       <c r="P51" t="b">
         <v>0</v>
@@ -3758,49 +3788,49 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>711</v>
+        <v>443</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C52">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D52" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F52">
-        <v>117932.1</v>
+        <v>134099</v>
       </c>
       <c r="G52">
-        <v>404.2</v>
+        <v>45.4</v>
       </c>
       <c r="H52">
-        <v>117889.035</v>
+        <v>134195.73000000001</v>
       </c>
       <c r="I52" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K52">
-        <v>16.86</v>
+        <v>1.6679999999999999</v>
       </c>
       <c r="L52">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N52">
-        <v>-43.064999999999998</v>
+        <v>96.73</v>
       </c>
       <c r="O52">
-        <v>2068</v>
+        <v>418</v>
       </c>
       <c r="P52" t="b">
         <v>0</v>
@@ -3811,49 +3841,49 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C53">
         <v>3.5</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E53" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="F53">
-        <v>137240.9</v>
+        <v>136591.4</v>
       </c>
       <c r="G53">
-        <v>404.2</v>
+        <v>23.8</v>
       </c>
       <c r="H53">
-        <v>137068.17499999999</v>
+        <v>136638.50700000001</v>
       </c>
       <c r="I53" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J53">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>3.5870000000000002</v>
+        <v>3.391</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N53">
-        <v>-172.72499999999999</v>
+        <v>47.106999999999999</v>
       </c>
       <c r="O53">
-        <v>2320</v>
+        <v>2298</v>
       </c>
       <c r="P53" t="b">
         <v>0</v>
@@ -3862,251 +3892,269 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>421</v>
+        <v>518</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="C54">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D54" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E54" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F54">
-        <v>134464</v>
+        <v>130042</v>
       </c>
       <c r="G54">
-        <v>87.9</v>
+        <v>91.5</v>
       </c>
       <c r="H54">
-        <v>134222.84700000001</v>
+        <v>129877.14599999999</v>
       </c>
       <c r="I54" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K54">
-        <v>1.5189999999999999</v>
+        <v>7.41</v>
       </c>
       <c r="L54">
         <v>4</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N54">
-        <v>-241.15299999999999</v>
+        <v>-164.85400000000001</v>
       </c>
       <c r="O54">
-        <v>2251</v>
+        <v>2201</v>
       </c>
       <c r="P54" t="b">
         <v>0</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
+      </c>
+      <c r="R54" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>492</v>
+        <v>269</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C55">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D55" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F55">
-        <v>132136</v>
+        <v>139026.9</v>
       </c>
       <c r="G55">
-        <v>87.9</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="H55">
-        <v>131861.98699999999</v>
+        <v>139249.27100000001</v>
       </c>
       <c r="I55" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J55">
         <v>2</v>
       </c>
       <c r="K55">
-        <v>0.91600000000000004</v>
+        <v>3.004</v>
       </c>
       <c r="L55">
         <v>4</v>
       </c>
       <c r="M55">
+        <v>4</v>
+      </c>
+      <c r="N55">
+        <v>222.37100000000001</v>
+      </c>
+      <c r="O55">
+        <v>2347</v>
+      </c>
+      <c r="P55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>418</v>
+      </c>
+      <c r="B56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56">
+        <v>7.5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F56">
+        <v>134489.29999999999</v>
+      </c>
+      <c r="G56">
+        <v>91.5</v>
+      </c>
+      <c r="H56">
+        <v>134475.166</v>
+      </c>
+      <c r="I56" t="s">
+        <v>26</v>
+      </c>
+      <c r="J56">
+        <v>8</v>
+      </c>
+      <c r="K56">
+        <v>6.0170000000000003</v>
+      </c>
+      <c r="L56">
+        <v>4</v>
+      </c>
+      <c r="M56">
         <v>2</v>
       </c>
-      <c r="N55">
-        <v>-274.01299999999998</v>
-      </c>
-      <c r="O55">
-        <v>2223</v>
-      </c>
-      <c r="P55" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>834</v>
-      </c>
-      <c r="B56" t="s">
-        <v>65</v>
-      </c>
-      <c r="C56">
-        <v>2.5</v>
-      </c>
-      <c r="D56" t="s">
-        <v>38</v>
-      </c>
-      <c r="E56" t="s">
-        <v>50</v>
-      </c>
-      <c r="F56">
-        <v>107743.5</v>
-      </c>
-      <c r="G56">
-        <v>61</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
+      <c r="N56">
+        <v>-14.134</v>
       </c>
       <c r="O56">
-        <v>2035</v>
+        <v>2254</v>
       </c>
       <c r="P56" t="b">
         <v>0</v>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>447</v>
+        <v>611</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C57">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F57">
-        <v>134001.60000000001</v>
+        <v>122933.4</v>
       </c>
       <c r="G57">
-        <v>87.9</v>
+        <v>42.3</v>
       </c>
       <c r="H57">
-        <v>134004.06700000001</v>
+        <v>122903.41099999999</v>
       </c>
       <c r="I57" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J57">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>3.8380000000000001</v>
+        <v>7.2709999999999999</v>
       </c>
       <c r="L57">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M57">
         <v>3</v>
       </c>
       <c r="N57">
-        <v>2.4670000000000001</v>
+        <v>-29.989000000000001</v>
       </c>
       <c r="O57">
-        <v>2235</v>
+        <v>365</v>
       </c>
       <c r="P57" t="b">
         <v>0</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
-      </c>
-      <c r="R57" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>389</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C58">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F58">
-        <v>135213.6</v>
+        <v>134076.9</v>
       </c>
       <c r="G58">
-        <v>87.9</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="H58">
-        <v>134998.38699999999</v>
+        <v>134187.851</v>
       </c>
       <c r="I58" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="K58">
-        <v>0.13600000000000001</v>
+        <v>0.433</v>
       </c>
       <c r="L58">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N58">
-        <v>-215.21299999999999</v>
+        <v>110.95099999999999</v>
       </c>
       <c r="O58">
-        <v>2273</v>
+        <v>2237</v>
       </c>
       <c r="P58" t="b">
         <v>0</v>
@@ -4117,52 +4165,52 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>441</v>
+        <v>735</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C59">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E59" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F59">
-        <v>134186.79999999999</v>
+        <v>116804.7</v>
       </c>
       <c r="G59">
-        <v>74.5</v>
+        <v>106.1</v>
       </c>
       <c r="H59">
-        <v>134074.41699999999</v>
+        <v>116927.75900000001</v>
       </c>
       <c r="I59" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K59">
-        <v>8.1660000000000004</v>
+        <v>6.2720000000000002</v>
       </c>
       <c r="L59">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N59">
-        <v>-112.383</v>
+        <v>123.059</v>
       </c>
       <c r="O59">
-        <v>2239</v>
+        <v>300</v>
       </c>
       <c r="P59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
@@ -4170,10 +4218,10 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>465</v>
+        <v>692</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C60">
         <v>3.5</v>
@@ -4182,40 +4230,40 @@
         <v>19</v>
       </c>
       <c r="E60" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F60">
-        <v>133412.29999999999</v>
+        <v>118504.2</v>
       </c>
       <c r="G60">
-        <v>103.6</v>
+        <v>42.3</v>
       </c>
       <c r="H60">
-        <v>133624.66899999999</v>
+        <v>118393.99099999999</v>
       </c>
       <c r="I60" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60">
-        <v>12.693</v>
+        <v>3.2480000000000002</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N60">
-        <v>212.369</v>
+        <v>-110.209</v>
       </c>
       <c r="O60">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="P60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="b">
         <v>0</v>
@@ -4223,63 +4271,45 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>799</v>
+        <v>716</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="C61">
         <v>3.5</v>
       </c>
       <c r="D61" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F61">
-        <v>111465.9</v>
+        <v>117761</v>
       </c>
       <c r="G61">
-        <v>61</v>
-      </c>
-      <c r="H61">
-        <v>111600.541</v>
-      </c>
-      <c r="I61" t="s">
-        <v>33</v>
+        <v>42.3</v>
       </c>
       <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>316</v>
+      </c>
+      <c r="P61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="b">
         <v>1</v>
-      </c>
-      <c r="K61">
-        <v>7.2089999999999996</v>
-      </c>
-      <c r="L61">
-        <v>7</v>
-      </c>
-      <c r="M61">
-        <v>3</v>
-      </c>
-      <c r="N61">
-        <v>134.64099999999999</v>
-      </c>
-      <c r="O61">
-        <v>2058</v>
-      </c>
-      <c r="P61" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>443</v>
+        <v>936</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="C62">
         <v>3.5</v>
@@ -4288,37 +4318,37 @@
         <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="F62">
-        <v>134099</v>
+        <v>84887</v>
       </c>
       <c r="G62">
-        <v>45.4</v>
+        <v>210.4</v>
       </c>
       <c r="H62">
-        <v>133964.28</v>
+        <v>85186.701000000001</v>
       </c>
       <c r="I62" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K62">
-        <v>1.843</v>
+        <v>17.706</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N62">
-        <v>-134.72</v>
+        <v>299.70100000000002</v>
       </c>
       <c r="O62">
-        <v>418</v>
+        <v>187</v>
       </c>
       <c r="P62" t="b">
         <v>0</v>
@@ -4329,375 +4359,372 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>345</v>
+        <v>713</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C63">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D63" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E63" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="F63">
-        <v>136591.4</v>
+        <v>117888.6</v>
       </c>
       <c r="G63">
-        <v>24</v>
-      </c>
-      <c r="H63">
-        <v>136638.50399999999</v>
-      </c>
-      <c r="I63" t="s">
-        <v>33</v>
+        <v>42.3</v>
       </c>
       <c r="J63">
-        <v>5</v>
-      </c>
-      <c r="K63">
-        <v>2.605</v>
-      </c>
-      <c r="L63">
-        <v>4</v>
-      </c>
-      <c r="M63">
-        <v>2</v>
-      </c>
-      <c r="N63">
-        <v>47.103999999999999</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>2298</v>
+        <v>319</v>
       </c>
       <c r="P63" t="b">
         <v>0</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
-      </c>
-      <c r="R63" t="s">
-        <v>88</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>518</v>
+        <v>558</v>
       </c>
       <c r="B64" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="C64">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D64" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F64">
-        <v>130042</v>
+        <v>126138.2</v>
       </c>
       <c r="G64">
-        <v>87.9</v>
+        <v>404.2</v>
       </c>
       <c r="H64">
-        <v>129877.147</v>
+        <v>125181.60400000001</v>
       </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J64">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K64">
-        <v>6.9809999999999999</v>
+        <v>1.1990000000000001</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M64">
         <v>4</v>
       </c>
       <c r="N64">
-        <v>-164.85300000000001</v>
+        <v>-956.596</v>
       </c>
       <c r="O64">
-        <v>2201</v>
+        <v>2173</v>
       </c>
       <c r="P64" t="b">
         <v>0</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
-      </c>
-      <c r="R64" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>319</v>
+        <v>915</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="C65">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="D65" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F65">
-        <v>136995</v>
+        <v>91039.2</v>
       </c>
       <c r="G65">
-        <v>87.9</v>
+        <v>215.8</v>
       </c>
       <c r="H65">
-        <v>136902.90700000001</v>
+        <v>90321.009000000005</v>
       </c>
       <c r="I65" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J65">
+        <v>4</v>
+      </c>
+      <c r="K65">
+        <v>11.762</v>
+      </c>
+      <c r="L65">
         <v>7</v>
       </c>
-      <c r="K65">
-        <v>3.5680000000000001</v>
-      </c>
-      <c r="L65">
-        <v>6</v>
-      </c>
       <c r="M65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N65">
-        <v>-92.093000000000004</v>
+        <v>-718.19100000000003</v>
       </c>
       <c r="O65">
-        <v>2317</v>
+        <v>208</v>
       </c>
       <c r="P65" t="b">
         <v>0</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
-      </c>
-      <c r="R65" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C66">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D66" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F66">
-        <v>136692.4</v>
+        <v>137083.5</v>
       </c>
       <c r="G66">
-        <v>87.9</v>
+        <v>91.5</v>
+      </c>
+      <c r="H66">
+        <v>136902.68599999999</v>
       </c>
       <c r="I66" t="s">
-        <v>93</v>
+        <v>26</v>
+      </c>
+      <c r="J66">
+        <v>7</v>
+      </c>
+      <c r="K66">
+        <v>9.42</v>
+      </c>
+      <c r="L66">
+        <v>6</v>
+      </c>
+      <c r="M66">
+        <v>3</v>
+      </c>
+      <c r="N66">
+        <v>-180.81399999999999</v>
       </c>
       <c r="O66">
-        <v>2309</v>
+        <v>2319</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
+      </c>
+      <c r="R66" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="C67">
         <v>4.5</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E67" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F67">
-        <v>139026.9</v>
+        <v>138572.70000000001</v>
       </c>
       <c r="G67">
-        <v>74.5</v>
-      </c>
-      <c r="I67" t="s">
-        <v>93</v>
+        <v>134</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>2347</v>
+        <v>2327</v>
       </c>
       <c r="P67" t="b">
         <v>0</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>611</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="C68">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E68" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F68">
-        <v>122933.4</v>
+        <v>135576.6</v>
       </c>
       <c r="G68">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="I68" t="s">
-        <v>93</v>
+        <v>79.599999999999994</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>365</v>
+        <v>2276</v>
       </c>
       <c r="P68" t="b">
         <v>0</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="C69">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
       </c>
       <c r="E69" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F69">
-        <v>72944.7</v>
+        <v>69366.399999999994</v>
       </c>
       <c r="G69">
-        <v>212.7</v>
+        <v>210.4</v>
       </c>
       <c r="H69">
-        <v>72705.869000000006</v>
+        <v>68890.201000000001</v>
       </c>
       <c r="I69" t="s">
         <v>21</v>
       </c>
       <c r="J69">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K69">
-        <v>13.077999999999999</v>
+        <v>16.585999999999999</v>
       </c>
       <c r="L69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N69">
-        <v>-238.83099999999999</v>
+        <v>-476.19900000000001</v>
       </c>
       <c r="O69">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
       </c>
       <c r="Q69" t="b">
         <v>0</v>
+      </c>
+      <c r="R69" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>735</v>
+        <v>824</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C70">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="D70" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E70" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F70">
-        <v>116804.7</v>
+        <v>108488.4</v>
       </c>
       <c r="G70">
-        <v>103.6</v>
+        <v>60.4</v>
       </c>
       <c r="H70">
-        <v>116927.749</v>
+        <v>108592.024</v>
       </c>
       <c r="I70" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>1.923</v>
+      </c>
+      <c r="L70">
         <v>5</v>
       </c>
-      <c r="K70">
-        <v>5.69</v>
-      </c>
-      <c r="L70">
-        <v>6</v>
-      </c>
       <c r="M70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N70">
-        <v>123.04900000000001</v>
+        <v>103.624</v>
       </c>
       <c r="O70">
-        <v>300</v>
+        <v>2044</v>
       </c>
       <c r="P70" t="b">
         <v>0</v>
@@ -4708,105 +4735,102 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>446</v>
+        <v>803</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="C71">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="D71" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E71" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="F71">
-        <v>134002</v>
+        <v>111244.7</v>
       </c>
       <c r="G71">
-        <v>87.9</v>
+        <v>60.4</v>
       </c>
       <c r="H71">
-        <v>134004.06700000001</v>
+        <v>111250.504</v>
       </c>
       <c r="I71" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J71">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K71">
-        <v>9.0839999999999996</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <v>2.0670000000000002</v>
+        <v>5.8040000000000003</v>
       </c>
       <c r="O71">
-        <v>2236</v>
+        <v>2057</v>
       </c>
       <c r="P71" t="b">
         <v>0</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
-      </c>
-      <c r="R71" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>445</v>
+        <v>658</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C72">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="D72" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E72" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F72">
-        <v>134076.9</v>
+        <v>120416.4</v>
       </c>
       <c r="G72">
-        <v>74.5</v>
+        <v>404.2</v>
       </c>
       <c r="H72">
-        <v>134074.25700000001</v>
+        <v>120805.38400000001</v>
       </c>
       <c r="I72" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J72">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K72">
-        <v>4.3899999999999997</v>
+        <v>3.5369999999999999</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M72">
         <v>3</v>
       </c>
       <c r="N72">
-        <v>-2.6429999999999998</v>
+        <v>388.98399999999998</v>
       </c>
       <c r="O72">
-        <v>2237</v>
+        <v>2093</v>
       </c>
       <c r="P72" t="b">
         <v>0</v>
@@ -4817,49 +4841,49 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>949</v>
+        <v>318</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C73">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="D73" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E73" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="F73">
-        <v>83488.399999999994</v>
+        <v>137023.4</v>
       </c>
       <c r="G73">
-        <v>112.5</v>
+        <v>91.5</v>
       </c>
       <c r="H73">
-        <v>83426.172000000006</v>
+        <v>136758.84599999999</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J73">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="K73">
-        <v>14.089</v>
+        <v>4.4820000000000002</v>
       </c>
       <c r="L73">
         <v>6</v>
       </c>
       <c r="M73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N73">
-        <v>-62.228000000000002</v>
+        <v>-264.55399999999997</v>
       </c>
       <c r="O73">
-        <v>174</v>
+        <v>2318</v>
       </c>
       <c r="P73" t="b">
         <v>0</v>
@@ -4870,102 +4894,105 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>692</v>
+        <v>321</v>
       </c>
       <c r="B74" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C74">
         <v>3.5</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E74" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F74">
-        <v>118504.2</v>
+        <v>136881.70000000001</v>
       </c>
       <c r="G74">
-        <v>32.200000000000003</v>
+        <v>91.5</v>
       </c>
       <c r="H74">
-        <v>118570.37</v>
+        <v>136902.70600000001</v>
       </c>
       <c r="I74" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K74">
-        <v>0.72199999999999998</v>
+        <v>6.5739999999999998</v>
       </c>
       <c r="L74">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N74">
-        <v>66.17</v>
+        <v>21.006</v>
       </c>
       <c r="O74">
-        <v>331</v>
+        <v>2315</v>
       </c>
       <c r="P74" t="b">
         <v>0</v>
       </c>
       <c r="Q74" t="b">
         <v>0</v>
+      </c>
+      <c r="R74" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>936</v>
+        <v>903</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="C75">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="D75" t="s">
         <v>19</v>
       </c>
       <c r="E75" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F75">
-        <v>84887</v>
+        <v>95551.5</v>
       </c>
       <c r="G75">
-        <v>212.7</v>
+        <v>215.8</v>
       </c>
       <c r="H75">
-        <v>85186.688999999998</v>
+        <v>95003.909</v>
       </c>
       <c r="I75" t="s">
         <v>21</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75">
-        <v>16.155999999999999</v>
+        <v>26.765999999999998</v>
       </c>
       <c r="L75">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N75">
-        <v>299.68900000000002</v>
+        <v>-547.59100000000001</v>
       </c>
       <c r="O75">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="P75" t="b">
         <v>0</v>
@@ -4976,49 +5003,49 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>713</v>
+        <v>252</v>
       </c>
       <c r="B76" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C76">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D76" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E76" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F76">
-        <v>117888.6</v>
+        <v>139805.29999999999</v>
       </c>
       <c r="G76">
-        <v>32.200000000000003</v>
+        <v>91.5</v>
       </c>
       <c r="H76">
-        <v>117815.35</v>
+        <v>139996.726</v>
       </c>
       <c r="I76" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>0.60599999999999998</v>
+        <v>1.8220000000000001</v>
       </c>
       <c r="L76">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M76">
         <v>2</v>
       </c>
       <c r="N76">
-        <v>-73.25</v>
+        <v>191.42599999999999</v>
       </c>
       <c r="O76">
-        <v>319</v>
+        <v>2360</v>
       </c>
       <c r="P76" t="b">
         <v>0</v>
@@ -5027,86 +5054,104 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>741</v>
+        <v>621</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C77">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D77" t="s">
         <v>19</v>
       </c>
       <c r="E77" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F77">
-        <v>116437.2</v>
+        <v>122593.3</v>
       </c>
       <c r="G77">
-        <v>32.200000000000003</v>
+        <v>106.1</v>
+      </c>
+      <c r="H77">
+        <v>122646.959</v>
+      </c>
+      <c r="I77" t="s">
+        <v>26</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>3.855</v>
+      </c>
+      <c r="L77">
+        <v>3</v>
+      </c>
+      <c r="M77">
+        <v>2</v>
+      </c>
+      <c r="N77">
+        <v>53.658999999999999</v>
       </c>
       <c r="O77">
-        <v>295</v>
+        <v>363</v>
       </c>
       <c r="P77" t="b">
         <v>0</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>558</v>
+        <v>339</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C78">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D78" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E78" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F78">
-        <v>126138.2</v>
+        <v>136605.70000000001</v>
       </c>
       <c r="G78">
-        <v>404.2</v>
+        <v>91.5</v>
       </c>
       <c r="H78">
-        <v>125181.595</v>
+        <v>136619.42600000001</v>
       </c>
       <c r="I78" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K78">
-        <v>1.512</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="L78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N78">
-        <v>-956.60500000000002</v>
+        <v>13.726000000000001</v>
       </c>
       <c r="O78">
-        <v>2173</v>
+        <v>2302</v>
       </c>
       <c r="P78" t="b">
         <v>0</v>
@@ -5117,317 +5162,314 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>915</v>
+        <v>376</v>
       </c>
       <c r="B79" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C79">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E79" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F79">
-        <v>91039.2</v>
+        <v>135975.5</v>
       </c>
       <c r="G79">
-        <v>177.3</v>
+        <v>404.2</v>
       </c>
       <c r="H79">
-        <v>91197.770999999993</v>
+        <v>134872.28400000001</v>
       </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J79">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K79">
-        <v>6.5640000000000001</v>
+        <v>5.431</v>
       </c>
       <c r="L79">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N79">
-        <v>158.571</v>
+        <v>-1103.2159999999999</v>
       </c>
       <c r="O79">
-        <v>208</v>
+        <v>2278</v>
       </c>
       <c r="P79" t="b">
         <v>0</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
-      </c>
-      <c r="R79" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>900</v>
+        <v>506</v>
       </c>
       <c r="B80" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="C80">
         <v>2.5</v>
       </c>
       <c r="D80" t="s">
+        <v>34</v>
+      </c>
+      <c r="E80" t="s">
+        <v>35</v>
+      </c>
+      <c r="F80">
+        <v>130935.4</v>
+      </c>
+      <c r="G80">
+        <v>91.5</v>
+      </c>
+      <c r="H80">
+        <v>131121.14600000001</v>
+      </c>
+      <c r="I80" t="s">
+        <v>26</v>
+      </c>
+      <c r="J80">
+        <v>7</v>
+      </c>
+      <c r="K80">
+        <v>1.4650000000000001</v>
+      </c>
+      <c r="L80">
+        <v>3</v>
+      </c>
+      <c r="M80">
+        <v>3</v>
+      </c>
+      <c r="N80">
+        <v>185.74600000000001</v>
+      </c>
+      <c r="O80">
+        <v>2209</v>
+      </c>
+      <c r="P80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>408</v>
+      </c>
+      <c r="B81" t="s">
+        <v>108</v>
+      </c>
+      <c r="C81">
+        <v>3.5</v>
+      </c>
+      <c r="D81" t="s">
+        <v>34</v>
+      </c>
+      <c r="E81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F81">
+        <v>134679.5</v>
+      </c>
+      <c r="G81">
+        <v>91.5</v>
+      </c>
+      <c r="H81">
+        <v>134393.14600000001</v>
+      </c>
+      <c r="I81" t="s">
+        <v>26</v>
+      </c>
+      <c r="J81">
+        <v>5</v>
+      </c>
+      <c r="K81">
+        <v>2.17</v>
+      </c>
+      <c r="L81">
+        <v>3</v>
+      </c>
+      <c r="M81">
+        <v>3</v>
+      </c>
+      <c r="N81">
+        <v>-286.35399999999998</v>
+      </c>
+      <c r="O81">
+        <v>2262</v>
+      </c>
+      <c r="P81" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>484</v>
+      </c>
+      <c r="B82" t="s">
+        <v>68</v>
+      </c>
+      <c r="C82">
+        <v>2.5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>34</v>
+      </c>
+      <c r="E82" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82">
+        <v>132788.5</v>
+      </c>
+      <c r="G82">
+        <v>91.5</v>
+      </c>
+      <c r="H82">
+        <v>132538.28599999999</v>
+      </c>
+      <c r="I82" t="s">
+        <v>26</v>
+      </c>
+      <c r="J82">
+        <v>7</v>
+      </c>
+      <c r="K82">
+        <v>3.1760000000000002</v>
+      </c>
+      <c r="L82">
+        <v>3</v>
+      </c>
+      <c r="M82">
+        <v>3</v>
+      </c>
+      <c r="N82">
+        <v>-250.214</v>
+      </c>
+      <c r="O82">
+        <v>2227</v>
+      </c>
+      <c r="P82" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>258</v>
+      </c>
+      <c r="B83" t="s">
+        <v>109</v>
+      </c>
+      <c r="C83">
+        <v>3.5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>34</v>
+      </c>
+      <c r="E83" t="s">
+        <v>87</v>
+      </c>
+      <c r="F83">
+        <v>139544.29999999999</v>
+      </c>
+      <c r="G83">
+        <v>23.8</v>
+      </c>
+      <c r="H83">
+        <v>139580.18700000001</v>
+      </c>
+      <c r="I83" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83">
+        <v>8</v>
+      </c>
+      <c r="K83">
+        <v>4.5949999999999998</v>
+      </c>
+      <c r="L83">
+        <v>3</v>
+      </c>
+      <c r="M83">
+        <v>2</v>
+      </c>
+      <c r="N83">
+        <v>35.887</v>
+      </c>
+      <c r="O83">
+        <v>2354</v>
+      </c>
+      <c r="P83" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>489</v>
+      </c>
+      <c r="B84" t="s">
+        <v>110</v>
+      </c>
+      <c r="C84">
+        <v>2.5</v>
+      </c>
+      <c r="D84" t="s">
         <v>19</v>
       </c>
-      <c r="E80" t="s">
-        <v>23</v>
-      </c>
-      <c r="F80">
-        <v>98148.6</v>
-      </c>
-      <c r="G80">
-        <v>177.3</v>
-      </c>
-      <c r="H80">
-        <v>97740.311000000002</v>
-      </c>
-      <c r="I80" t="s">
-        <v>21</v>
-      </c>
-      <c r="J80">
+      <c r="E84" t="s">
+        <v>62</v>
+      </c>
+      <c r="F84">
+        <v>132356.79999999999</v>
+      </c>
+      <c r="G84">
+        <v>106.1</v>
+      </c>
+      <c r="H84">
+        <v>132260.61900000001</v>
+      </c>
+      <c r="I84" t="s">
+        <v>50</v>
+      </c>
+      <c r="J84">
         <v>3</v>
       </c>
-      <c r="K80">
-        <v>22.936</v>
-      </c>
-      <c r="L80">
-        <v>10</v>
-      </c>
-      <c r="M80">
-        <v>9</v>
-      </c>
-      <c r="N80">
-        <v>-408.28899999999999</v>
-      </c>
-      <c r="O80">
-        <v>223</v>
-      </c>
-      <c r="P80" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>299</v>
-      </c>
-      <c r="B81" t="s">
-        <v>56</v>
-      </c>
-      <c r="C81">
-        <v>4.5</v>
-      </c>
-      <c r="D81" t="s">
-        <v>38</v>
-      </c>
-      <c r="E81" t="s">
-        <v>57</v>
-      </c>
-      <c r="F81">
-        <v>138572.70000000001</v>
-      </c>
-      <c r="G81">
-        <v>132.1</v>
-      </c>
-      <c r="H81">
-        <v>138832.073</v>
-      </c>
-      <c r="I81" t="s">
-        <v>33</v>
-      </c>
-      <c r="J81">
-        <v>2</v>
-      </c>
-      <c r="K81">
-        <v>0.52200000000000002</v>
-      </c>
-      <c r="L81">
-        <v>6</v>
-      </c>
-      <c r="M81">
-        <v>2</v>
-      </c>
-      <c r="N81">
-        <v>259.37299999999999</v>
-      </c>
-      <c r="O81">
-        <v>2327</v>
-      </c>
-      <c r="P81" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>1014</v>
-      </c>
-      <c r="B82" t="s">
-        <v>103</v>
-      </c>
-      <c r="C82">
-        <v>1.5</v>
-      </c>
-      <c r="D82" t="s">
-        <v>19</v>
-      </c>
-      <c r="E82" t="s">
-        <v>28</v>
-      </c>
-      <c r="F82">
-        <v>69366.399999999994</v>
-      </c>
-      <c r="G82">
-        <v>212.7</v>
-      </c>
-      <c r="H82">
-        <v>68890.188999999998</v>
-      </c>
-      <c r="I82" t="s">
-        <v>21</v>
-      </c>
-      <c r="J82">
-        <v>14</v>
-      </c>
-      <c r="K82">
-        <v>16.437999999999999</v>
-      </c>
-      <c r="L82">
-        <v>7</v>
-      </c>
-      <c r="M82">
-        <v>5</v>
-      </c>
-      <c r="N82">
-        <v>-476.21100000000001</v>
-      </c>
-      <c r="O82">
-        <v>110</v>
-      </c>
-      <c r="P82" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>381</v>
-      </c>
-      <c r="B83" t="s">
-        <v>71</v>
-      </c>
-      <c r="C83">
-        <v>2.5</v>
-      </c>
-      <c r="D83" t="s">
-        <v>38</v>
-      </c>
-      <c r="E83" t="s">
-        <v>48</v>
-      </c>
-      <c r="F83">
-        <v>135576.6</v>
-      </c>
-      <c r="G83">
-        <v>74.5</v>
-      </c>
-      <c r="H83">
-        <v>135482.057</v>
-      </c>
-      <c r="I83" t="s">
-        <v>33</v>
-      </c>
-      <c r="J83">
-        <v>2</v>
-      </c>
-      <c r="K83">
-        <v>1.5009999999999999</v>
-      </c>
-      <c r="L83">
-        <v>7</v>
-      </c>
-      <c r="M83">
-        <v>5</v>
-      </c>
-      <c r="N83">
-        <v>-94.543000000000006</v>
-      </c>
-      <c r="O83">
-        <v>2276</v>
-      </c>
-      <c r="P83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>803</v>
-      </c>
-      <c r="B84" t="s">
-        <v>104</v>
-      </c>
-      <c r="C84">
-        <v>4.5</v>
-      </c>
-      <c r="D84" t="s">
-        <v>38</v>
-      </c>
-      <c r="E84" t="s">
-        <v>50</v>
-      </c>
-      <c r="F84">
-        <v>111244.7</v>
-      </c>
-      <c r="G84">
-        <v>61</v>
-      </c>
-      <c r="H84">
-        <v>111250.501</v>
-      </c>
-      <c r="I84" t="s">
-        <v>105</v>
-      </c>
-      <c r="J84">
-        <v>1</v>
-      </c>
       <c r="K84">
-        <v>0.27200000000000002</v>
+        <v>3.8719999999999999</v>
       </c>
       <c r="L84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M84">
         <v>1</v>
       </c>
       <c r="N84">
-        <v>5.8010000000000002</v>
+        <v>-96.180999999999997</v>
       </c>
       <c r="O84">
-        <v>2057</v>
+        <v>384</v>
       </c>
       <c r="P84" t="b">
         <v>0</v>
@@ -5436,263 +5478,245 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>824</v>
+        <v>402</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C85">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D85" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E85" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F85">
-        <v>108488.4</v>
+        <v>134848.29999999999</v>
       </c>
       <c r="G85">
-        <v>61</v>
+        <v>134</v>
       </c>
       <c r="H85">
-        <v>108592.02099999999</v>
+        <v>134546.08799999999</v>
       </c>
       <c r="I85" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J85">
+        <v>6</v>
+      </c>
+      <c r="K85">
+        <v>2.161</v>
+      </c>
+      <c r="L85">
+        <v>3</v>
+      </c>
+      <c r="M85">
+        <v>2</v>
+      </c>
+      <c r="N85">
+        <v>-302.21199999999999</v>
+      </c>
+      <c r="O85">
+        <v>2265</v>
+      </c>
+      <c r="P85" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>209</v>
+      </c>
+      <c r="B86" t="s">
+        <v>111</v>
+      </c>
+      <c r="C86">
+        <v>5.5</v>
+      </c>
+      <c r="D86" t="s">
+        <v>34</v>
+      </c>
+      <c r="E86" t="s">
+        <v>87</v>
+      </c>
+      <c r="F86">
+        <v>140979.5</v>
+      </c>
+      <c r="G86">
+        <v>23.8</v>
+      </c>
+      <c r="H86">
+        <v>140917.04699999999</v>
+      </c>
+      <c r="I86" t="s">
+        <v>26</v>
+      </c>
+      <c r="J86">
+        <v>2</v>
+      </c>
+      <c r="K86">
+        <v>4.2050000000000001</v>
+      </c>
+      <c r="L86">
+        <v>3</v>
+      </c>
+      <c r="M86">
+        <v>3</v>
+      </c>
+      <c r="N86">
+        <v>-62.453000000000003</v>
+      </c>
+      <c r="O86">
+        <v>2383</v>
+      </c>
+      <c r="P86" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>212</v>
+      </c>
+      <c r="B87" t="s">
+        <v>112</v>
+      </c>
+      <c r="C87">
+        <v>6.5</v>
+      </c>
+      <c r="D87" t="s">
+        <v>34</v>
+      </c>
+      <c r="E87" t="s">
+        <v>87</v>
+      </c>
+      <c r="F87">
+        <v>140972</v>
+      </c>
+      <c r="G87">
+        <v>23.8</v>
+      </c>
+      <c r="H87">
+        <v>140998.587</v>
+      </c>
+      <c r="I87" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87">
+        <v>7</v>
+      </c>
+      <c r="K87">
+        <v>2.9140000000000001</v>
+      </c>
+      <c r="L87">
+        <v>3</v>
+      </c>
+      <c r="M87">
+        <v>3</v>
+      </c>
+      <c r="N87">
+        <v>26.587</v>
+      </c>
+      <c r="O87">
+        <v>2381</v>
+      </c>
+      <c r="P87" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>254</v>
+      </c>
+      <c r="B88" t="s">
+        <v>113</v>
+      </c>
+      <c r="C88">
+        <v>5.5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>34</v>
+      </c>
+      <c r="E88" t="s">
+        <v>87</v>
+      </c>
+      <c r="F88">
+        <v>139570.6</v>
+      </c>
+      <c r="G88">
+        <v>23.8</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>2358</v>
+      </c>
+      <c r="P88" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="b">
         <v>1</v>
       </c>
-      <c r="K85">
-        <v>2.0270000000000001</v>
-      </c>
-      <c r="L85">
-        <v>5</v>
-      </c>
-      <c r="M85">
-        <v>3</v>
-      </c>
-      <c r="N85">
-        <v>103.621</v>
-      </c>
-      <c r="O85">
-        <v>2044</v>
-      </c>
-      <c r="P85" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>406</v>
-      </c>
-      <c r="B86" t="s">
-        <v>60</v>
-      </c>
-      <c r="C86">
-        <v>4.5</v>
-      </c>
-      <c r="D86" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" t="s">
-        <v>39</v>
-      </c>
-      <c r="F86">
-        <v>134714.79999999999</v>
-      </c>
-      <c r="G86">
-        <v>87.9</v>
-      </c>
-      <c r="H86">
-        <v>134696.62700000001</v>
-      </c>
-      <c r="I86" t="s">
-        <v>21</v>
-      </c>
-      <c r="J86">
-        <v>4</v>
-      </c>
-      <c r="K86">
-        <v>6.6550000000000002</v>
-      </c>
-      <c r="L86">
-        <v>4</v>
-      </c>
-      <c r="M86">
-        <v>4</v>
-      </c>
-      <c r="N86">
-        <v>-18.172999999999998</v>
-      </c>
-      <c r="O86">
-        <v>2263</v>
-      </c>
-      <c r="P86" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>658</v>
-      </c>
-      <c r="B87" t="s">
-        <v>75</v>
-      </c>
-      <c r="C87">
-        <v>5.5</v>
-      </c>
-      <c r="D87" t="s">
-        <v>38</v>
-      </c>
-      <c r="E87" t="s">
-        <v>55</v>
-      </c>
-      <c r="F87">
-        <v>120416.4</v>
-      </c>
-      <c r="G87">
-        <v>404.2</v>
-      </c>
-      <c r="H87">
-        <v>120805.375</v>
-      </c>
-      <c r="I87" t="s">
-        <v>33</v>
-      </c>
-      <c r="J87">
-        <v>11</v>
-      </c>
-      <c r="K87">
-        <v>5.1689999999999996</v>
-      </c>
-      <c r="L87">
-        <v>7</v>
-      </c>
-      <c r="M87">
-        <v>4</v>
-      </c>
-      <c r="N87">
-        <v>388.97500000000002</v>
-      </c>
-      <c r="O87">
-        <v>2093</v>
-      </c>
-      <c r="P87" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>856</v>
-      </c>
-      <c r="B88" t="s">
-        <v>107</v>
-      </c>
-      <c r="C88">
-        <v>2.5</v>
-      </c>
-      <c r="D88" t="s">
-        <v>38</v>
-      </c>
-      <c r="E88" t="s">
-        <v>50</v>
-      </c>
-      <c r="F88">
-        <v>105790.1</v>
-      </c>
-      <c r="G88">
-        <v>61</v>
-      </c>
-      <c r="H88">
-        <v>105721.30100000001</v>
-      </c>
-      <c r="I88" t="s">
-        <v>33</v>
-      </c>
-      <c r="J88">
-        <v>4</v>
-      </c>
-      <c r="K88">
-        <v>3.1059999999999999</v>
-      </c>
-      <c r="L88">
-        <v>5</v>
-      </c>
-      <c r="M88">
-        <v>3</v>
-      </c>
-      <c r="N88">
-        <v>-68.799000000000007</v>
-      </c>
-      <c r="O88">
-        <v>2013</v>
-      </c>
-      <c r="P88" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>392</v>
+        <v>324</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C89">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D89" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E89" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F89">
-        <v>135131.5</v>
+        <v>136778</v>
       </c>
       <c r="G89">
-        <v>87.9</v>
+        <v>91.5</v>
       </c>
       <c r="H89">
-        <v>135325.38699999999</v>
+        <v>136783.86600000001</v>
       </c>
       <c r="I89" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J89">
+        <v>16</v>
+      </c>
+      <c r="K89">
+        <v>2.3940000000000001</v>
+      </c>
+      <c r="L89">
         <v>2</v>
-      </c>
-      <c r="K89">
-        <v>0.39300000000000002</v>
-      </c>
-      <c r="L89">
-        <v>3</v>
       </c>
       <c r="M89">
         <v>2</v>
       </c>
       <c r="N89">
-        <v>193.887</v>
+        <v>5.8659999999999997</v>
       </c>
       <c r="O89">
-        <v>2271</v>
+        <v>2313</v>
       </c>
       <c r="P89" t="b">
         <v>0</v>
@@ -5701,51 +5725,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>318</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="C90">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="D90" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E90" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F90">
-        <v>137023.4</v>
+        <v>132069.6</v>
       </c>
       <c r="G90">
-        <v>87.9</v>
+        <v>91.5</v>
       </c>
       <c r="H90">
-        <v>136758.84700000001</v>
+        <v>132205.42600000001</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J90">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K90">
-        <v>6.6059999999999999</v>
+        <v>5.4710000000000001</v>
       </c>
       <c r="L90">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M90">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N90">
-        <v>-264.553</v>
+        <v>135.82599999999999</v>
       </c>
       <c r="O90">
-        <v>2318</v>
+        <v>2220</v>
       </c>
       <c r="P90" t="b">
         <v>0</v>
@@ -5754,921 +5778,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>1093</v>
-      </c>
-      <c r="B91" t="s">
-        <v>109</v>
-      </c>
-      <c r="C91">
-        <v>0.5</v>
-      </c>
-      <c r="D91" t="s">
-        <v>38</v>
-      </c>
-      <c r="E91" t="s">
-        <v>110</v>
-      </c>
-      <c r="F91">
-        <v>49610.2</v>
-      </c>
-      <c r="G91">
-        <v>98.6</v>
-      </c>
-      <c r="H91">
-        <v>49653.82</v>
-      </c>
-      <c r="I91" t="s">
-        <v>21</v>
-      </c>
-      <c r="J91">
-        <v>6</v>
-      </c>
-      <c r="K91">
-        <v>30.27</v>
-      </c>
-      <c r="L91">
-        <v>7</v>
-      </c>
-      <c r="M91">
-        <v>7</v>
-      </c>
-      <c r="N91">
-        <v>43.62</v>
-      </c>
-      <c r="O91">
-        <v>1966</v>
-      </c>
-      <c r="P91" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>321</v>
-      </c>
-      <c r="B92" t="s">
-        <v>111</v>
-      </c>
-      <c r="C92">
-        <v>3.5</v>
-      </c>
-      <c r="D92" t="s">
-        <v>38</v>
-      </c>
-      <c r="E92" t="s">
-        <v>39</v>
-      </c>
-      <c r="F92">
-        <v>136881.70000000001</v>
-      </c>
-      <c r="G92">
-        <v>87.9</v>
-      </c>
-      <c r="H92">
-        <v>136902.927</v>
-      </c>
-      <c r="I92" t="s">
-        <v>33</v>
-      </c>
-      <c r="J92">
-        <v>5</v>
-      </c>
-      <c r="K92">
-        <v>5.8810000000000002</v>
-      </c>
-      <c r="L92">
-        <v>7</v>
-      </c>
-      <c r="M92">
-        <v>4</v>
-      </c>
-      <c r="N92">
-        <v>21.227</v>
-      </c>
-      <c r="O92">
-        <v>2315</v>
-      </c>
-      <c r="P92" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="b">
-        <v>0</v>
-      </c>
-      <c r="R92" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>479</v>
-      </c>
-      <c r="B93" t="s">
-        <v>113</v>
-      </c>
-      <c r="C93">
-        <v>4.5</v>
-      </c>
-      <c r="D93" t="s">
-        <v>19</v>
-      </c>
-      <c r="E93" t="s">
-        <v>20</v>
-      </c>
-      <c r="F93">
-        <v>132959.20000000001</v>
-      </c>
-      <c r="G93">
-        <v>103.6</v>
-      </c>
-      <c r="H93">
-        <v>132903.46900000001</v>
-      </c>
-      <c r="I93" t="s">
-        <v>21</v>
-      </c>
-      <c r="J93">
-        <v>2</v>
-      </c>
-      <c r="K93">
-        <v>9.4410000000000007</v>
-      </c>
-      <c r="L93">
-        <v>7</v>
-      </c>
-      <c r="M93">
-        <v>4</v>
-      </c>
-      <c r="N93">
-        <v>-55.731000000000002</v>
-      </c>
-      <c r="O93">
-        <v>392</v>
-      </c>
-      <c r="P93" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>903</v>
-      </c>
-      <c r="B94" t="s">
-        <v>102</v>
-      </c>
-      <c r="C94">
-        <v>1.5</v>
-      </c>
-      <c r="D94" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" t="s">
-        <v>23</v>
-      </c>
-      <c r="F94">
-        <v>95551.5</v>
-      </c>
-      <c r="G94">
-        <v>177.3</v>
-      </c>
-      <c r="H94">
-        <v>95003.910999999993</v>
-      </c>
-      <c r="I94" t="s">
-        <v>21</v>
-      </c>
-      <c r="J94">
-        <v>5</v>
-      </c>
-      <c r="K94">
-        <v>25.433</v>
-      </c>
-      <c r="L94">
-        <v>10</v>
-      </c>
-      <c r="M94">
-        <v>8</v>
-      </c>
-      <c r="N94">
-        <v>-547.58900000000006</v>
-      </c>
-      <c r="O94">
-        <v>220</v>
-      </c>
-      <c r="P94" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>621</v>
-      </c>
-      <c r="B95" t="s">
-        <v>62</v>
-      </c>
-      <c r="C95">
-        <v>1.5</v>
-      </c>
-      <c r="D95" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" t="s">
-        <v>20</v>
-      </c>
-      <c r="F95">
-        <v>122593.3</v>
-      </c>
-      <c r="G95">
-        <v>103.6</v>
-      </c>
-      <c r="H95">
-        <v>122646.94899999999</v>
-      </c>
-      <c r="I95" t="s">
-        <v>33</v>
-      </c>
-      <c r="J95">
-        <v>1</v>
-      </c>
-      <c r="K95">
-        <v>3.36</v>
-      </c>
-      <c r="L95">
-        <v>4</v>
-      </c>
-      <c r="M95">
-        <v>2</v>
-      </c>
-      <c r="N95">
-        <v>53.649000000000001</v>
-      </c>
-      <c r="O95">
-        <v>363</v>
-      </c>
-      <c r="P95" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>252</v>
-      </c>
-      <c r="B96" t="s">
-        <v>114</v>
-      </c>
-      <c r="C96">
-        <v>4.5</v>
-      </c>
-      <c r="D96" t="s">
-        <v>38</v>
-      </c>
-      <c r="E96" t="s">
-        <v>39</v>
-      </c>
-      <c r="F96">
-        <v>139805.29999999999</v>
-      </c>
-      <c r="G96">
-        <v>87.9</v>
-      </c>
-      <c r="H96">
-        <v>139996.70699999999</v>
-      </c>
-      <c r="I96" t="s">
-        <v>33</v>
-      </c>
-      <c r="J96">
-        <v>4</v>
-      </c>
-      <c r="K96">
-        <v>1.599</v>
-      </c>
-      <c r="L96">
-        <v>2</v>
-      </c>
-      <c r="M96">
-        <v>2</v>
-      </c>
-      <c r="N96">
-        <v>191.40700000000001</v>
-      </c>
-      <c r="O96">
-        <v>2360</v>
-      </c>
-      <c r="P96" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>339</v>
-      </c>
-      <c r="B97" t="s">
-        <v>108</v>
-      </c>
-      <c r="C97">
-        <v>2.5</v>
-      </c>
-      <c r="D97" t="s">
-        <v>38</v>
-      </c>
-      <c r="E97" t="s">
-        <v>39</v>
-      </c>
-      <c r="F97">
-        <v>136605.70000000001</v>
-      </c>
-      <c r="G97">
-        <v>87.9</v>
-      </c>
-      <c r="H97">
-        <v>136728.76699999999</v>
-      </c>
-      <c r="I97" t="s">
-        <v>33</v>
-      </c>
-      <c r="J97">
-        <v>8</v>
-      </c>
-      <c r="K97">
-        <v>1.329</v>
-      </c>
-      <c r="L97">
-        <v>5</v>
-      </c>
-      <c r="M97">
-        <v>4</v>
-      </c>
-      <c r="N97">
-        <v>123.06699999999999</v>
-      </c>
-      <c r="O97">
-        <v>2302</v>
-      </c>
-      <c r="P97" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="b">
-        <v>0</v>
-      </c>
-      <c r="R97" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>376</v>
-      </c>
-      <c r="B98" t="s">
-        <v>54</v>
-      </c>
-      <c r="C98">
-        <v>6.5</v>
-      </c>
-      <c r="D98" t="s">
-        <v>38</v>
-      </c>
-      <c r="E98" t="s">
-        <v>55</v>
-      </c>
-      <c r="F98">
-        <v>135975.5</v>
-      </c>
-      <c r="G98">
-        <v>404.2</v>
-      </c>
-      <c r="H98">
-        <v>134872.29500000001</v>
-      </c>
-      <c r="I98" t="s">
-        <v>33</v>
-      </c>
-      <c r="J98">
-        <v>19</v>
-      </c>
-      <c r="K98">
-        <v>6.51</v>
-      </c>
-      <c r="L98">
-        <v>3</v>
-      </c>
-      <c r="M98">
-        <v>3</v>
-      </c>
-      <c r="N98">
-        <v>-1103.2049999999999</v>
-      </c>
-      <c r="O98">
-        <v>2278</v>
-      </c>
-      <c r="P98" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>506</v>
-      </c>
-      <c r="B99" t="s">
-        <v>78</v>
-      </c>
-      <c r="C99">
-        <v>2.5</v>
-      </c>
-      <c r="D99" t="s">
-        <v>38</v>
-      </c>
-      <c r="E99" t="s">
-        <v>39</v>
-      </c>
-      <c r="F99">
-        <v>130935.4</v>
-      </c>
-      <c r="G99">
-        <v>87.9</v>
-      </c>
-      <c r="H99">
-        <v>130744.947</v>
-      </c>
-      <c r="I99" t="s">
-        <v>33</v>
-      </c>
-      <c r="J99">
-        <v>8</v>
-      </c>
-      <c r="K99">
-        <v>1.0940000000000001</v>
-      </c>
-      <c r="L99">
-        <v>3</v>
-      </c>
-      <c r="M99">
-        <v>2</v>
-      </c>
-      <c r="N99">
-        <v>-190.453</v>
-      </c>
-      <c r="O99">
-        <v>2209</v>
-      </c>
-      <c r="P99" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>418</v>
-      </c>
-      <c r="B100" t="s">
-        <v>116</v>
-      </c>
-      <c r="C100">
-        <v>7.5</v>
-      </c>
-      <c r="D100" t="s">
-        <v>38</v>
-      </c>
-      <c r="E100" t="s">
-        <v>39</v>
-      </c>
-      <c r="F100">
-        <v>134489.29999999999</v>
-      </c>
-      <c r="G100">
-        <v>87.9</v>
-      </c>
-      <c r="H100">
-        <v>134475.16699999999</v>
-      </c>
-      <c r="I100" t="s">
-        <v>33</v>
-      </c>
-      <c r="J100">
-        <v>8</v>
-      </c>
-      <c r="K100">
-        <v>7.6609999999999996</v>
-      </c>
-      <c r="L100">
-        <v>4</v>
-      </c>
-      <c r="M100">
-        <v>2</v>
-      </c>
-      <c r="N100">
-        <v>-14.132999999999999</v>
-      </c>
-      <c r="O100">
-        <v>2254</v>
-      </c>
-      <c r="P100" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>484</v>
-      </c>
-      <c r="B101" t="s">
-        <v>80</v>
-      </c>
-      <c r="C101">
-        <v>2.5</v>
-      </c>
-      <c r="D101" t="s">
-        <v>38</v>
-      </c>
-      <c r="E101" t="s">
-        <v>39</v>
-      </c>
-      <c r="F101">
-        <v>132788.5</v>
-      </c>
-      <c r="G101">
-        <v>87.9</v>
-      </c>
-      <c r="H101">
-        <v>132566.247</v>
-      </c>
-      <c r="I101" t="s">
-        <v>33</v>
-      </c>
-      <c r="J101">
-        <v>8</v>
-      </c>
-      <c r="K101">
-        <v>1.615</v>
-      </c>
-      <c r="L101">
-        <v>3</v>
-      </c>
-      <c r="M101">
-        <v>2</v>
-      </c>
-      <c r="N101">
-        <v>-222.25299999999999</v>
-      </c>
-      <c r="O101">
-        <v>2227</v>
-      </c>
-      <c r="P101" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>489</v>
-      </c>
-      <c r="B102" t="s">
-        <v>113</v>
-      </c>
-      <c r="C102">
-        <v>2.5</v>
-      </c>
-      <c r="D102" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" t="s">
-        <v>20</v>
-      </c>
-      <c r="F102">
-        <v>132356.79999999999</v>
-      </c>
-      <c r="G102">
-        <v>103.6</v>
-      </c>
-      <c r="H102">
-        <v>132260.50899999999</v>
-      </c>
-      <c r="I102" t="s">
-        <v>33</v>
-      </c>
-      <c r="J102">
-        <v>2</v>
-      </c>
-      <c r="K102">
-        <v>4.3090000000000002</v>
-      </c>
-      <c r="L102">
-        <v>6</v>
-      </c>
-      <c r="M102">
-        <v>2</v>
-      </c>
-      <c r="N102">
-        <v>-96.290999999999997</v>
-      </c>
-      <c r="O102">
-        <v>384</v>
-      </c>
-      <c r="P102" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>212</v>
-      </c>
-      <c r="B103" t="s">
-        <v>117</v>
-      </c>
-      <c r="C103">
-        <v>6.5</v>
-      </c>
-      <c r="D103" t="s">
-        <v>38</v>
-      </c>
-      <c r="E103" t="s">
-        <v>87</v>
-      </c>
-      <c r="F103">
-        <v>140972</v>
-      </c>
-      <c r="G103">
-        <v>24</v>
-      </c>
-      <c r="H103">
-        <v>140942.82399999999</v>
-      </c>
-      <c r="I103" t="s">
-        <v>33</v>
-      </c>
-      <c r="J103">
-        <v>6</v>
-      </c>
-      <c r="K103">
-        <v>3.7839999999999998</v>
-      </c>
-      <c r="L103">
-        <v>3</v>
-      </c>
-      <c r="M103">
-        <v>3</v>
-      </c>
-      <c r="N103">
-        <v>-29.175999999999998</v>
-      </c>
-      <c r="O103">
-        <v>2381</v>
-      </c>
-      <c r="P103" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>402</v>
-      </c>
-      <c r="B104" t="s">
-        <v>56</v>
-      </c>
-      <c r="C104">
-        <v>1.5</v>
-      </c>
-      <c r="D104" t="s">
-        <v>38</v>
-      </c>
-      <c r="E104" t="s">
-        <v>57</v>
-      </c>
-      <c r="F104">
-        <v>134848.29999999999</v>
-      </c>
-      <c r="G104">
-        <v>132.1</v>
-      </c>
-      <c r="H104">
-        <v>134645.81299999999</v>
-      </c>
-      <c r="I104" t="s">
-        <v>33</v>
-      </c>
-      <c r="J104">
-        <v>8</v>
-      </c>
-      <c r="K104">
-        <v>2.6469999999999998</v>
-      </c>
-      <c r="L104">
-        <v>3</v>
-      </c>
-      <c r="M104">
-        <v>2</v>
-      </c>
-      <c r="N104">
-        <v>-202.48699999999999</v>
-      </c>
-      <c r="O104">
-        <v>2265</v>
-      </c>
-      <c r="P104" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>209</v>
-      </c>
-      <c r="B105" t="s">
-        <v>118</v>
-      </c>
-      <c r="C105">
-        <v>5.5</v>
-      </c>
-      <c r="D105" t="s">
-        <v>38</v>
-      </c>
-      <c r="E105" t="s">
-        <v>87</v>
-      </c>
-      <c r="F105">
-        <v>140979.5</v>
-      </c>
-      <c r="G105">
-        <v>24</v>
-      </c>
-      <c r="H105">
-        <v>140917.04399999999</v>
-      </c>
-      <c r="I105" t="s">
-        <v>33</v>
-      </c>
-      <c r="J105">
-        <v>2</v>
-      </c>
-      <c r="K105">
-        <v>3.327</v>
-      </c>
-      <c r="L105">
-        <v>4</v>
-      </c>
-      <c r="M105">
-        <v>3</v>
-      </c>
-      <c r="N105">
-        <v>-62.456000000000003</v>
-      </c>
-      <c r="O105">
-        <v>2383</v>
-      </c>
-      <c r="P105" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>254</v>
-      </c>
-      <c r="B106" t="s">
-        <v>119</v>
-      </c>
-      <c r="C106">
-        <v>5.5</v>
-      </c>
-      <c r="D106" t="s">
-        <v>38</v>
-      </c>
-      <c r="E106" t="s">
-        <v>87</v>
-      </c>
-      <c r="F106">
-        <v>139570.6</v>
-      </c>
-      <c r="G106">
-        <v>24</v>
-      </c>
-      <c r="H106">
-        <v>139554.264</v>
-      </c>
-      <c r="I106" t="s">
-        <v>33</v>
-      </c>
-      <c r="J106">
-        <v>1</v>
-      </c>
-      <c r="K106">
-        <v>0.56200000000000006</v>
-      </c>
-      <c r="L106">
-        <v>2</v>
-      </c>
-      <c r="M106">
-        <v>2</v>
-      </c>
-      <c r="N106">
-        <v>-16.335999999999999</v>
-      </c>
-      <c r="O106">
-        <v>2358</v>
-      </c>
-      <c r="P106" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>495</v>
-      </c>
-      <c r="B107" t="s">
-        <v>44</v>
-      </c>
-      <c r="C107">
-        <v>7.5</v>
-      </c>
-      <c r="D107" t="s">
-        <v>38</v>
-      </c>
-      <c r="E107" t="s">
-        <v>39</v>
-      </c>
-      <c r="F107">
-        <v>132069.6</v>
-      </c>
-      <c r="G107">
-        <v>87.9</v>
-      </c>
-      <c r="H107">
-        <v>132205.40700000001</v>
-      </c>
-      <c r="I107" t="s">
-        <v>33</v>
-      </c>
-      <c r="J107">
-        <v>15</v>
-      </c>
-      <c r="K107">
-        <v>5.5659999999999998</v>
-      </c>
-      <c r="L107">
-        <v>2</v>
-      </c>
-      <c r="M107">
-        <v>2</v>
-      </c>
-      <c r="N107">
-        <v>135.80699999999999</v>
-      </c>
-      <c r="O107">
-        <v>2220</v>
-      </c>
-      <c r="P107" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R107" xr:uid="{1FE5B977-2EE7-4A64-B665-59414AEBC9CA}">
-    <filterColumn colId="16">
-      <filters>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R90" xr:uid="{CEE7B52F-37E9-4757-BFB2-50AE26839FFD}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/LineClass/found_levels.xlsx
+++ b/LineClass/found_levels.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UMD\AI\as-ai\LineClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C241C9A-D178-4FE7-99DF-FB8C0ACD8F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6F8EB393-5B3F-4A15-93DD-E88B7A8D705D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="1425" windowWidth="50130" windowHeight="17505" xr2:uid="{E743DC57-3E0B-40B1-BC6B-EF7851EBEC40}"/>
   </bookViews>
   <sheets>
     <sheet name="found_levels" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">found_levels!$A$1:$R$90</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="116">
   <si>
     <t>idx</t>
   </si>
@@ -241,9 +242,6 @@
     <t>f27d _3F2H</t>
   </si>
   <si>
-    <t>duplicate with row 317 (J 4.5), 0.000 cm^-1 away; duplicate with row 321 (J 3.5), 0.020 cm^-1 away</t>
-  </si>
-  <si>
     <t>f27d _3F4G</t>
   </si>
   <si>
@@ -365,6 +363,15 @@
   </si>
   <si>
     <t>f25g _3F2I</t>
+  </si>
+  <si>
+    <t>Accepted!</t>
+  </si>
+  <si>
+    <t>Too large dE_o_c; Accepted!</t>
+  </si>
+  <si>
+    <t>duplicate with row 317 (J 4.5), 0.000 cm^-1 away; duplicate with row 321 (J 3.5), 0.020 cm^-1 away; accepted.</t>
   </si>
 </sst>
 </file>
@@ -507,7 +514,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -687,6 +694,24 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -848,8 +873,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1225,6 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE7B52F-37E9-4757-BFB2-50AE26839FFD}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1360,7 +1389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>986</v>
       </c>
@@ -1395,7 +1424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>951</v>
       </c>
@@ -1500,6 +1529,9 @@
       <c r="Q5" t="b">
         <v>0</v>
       </c>
+      <c r="R5" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -1557,7 +1589,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>691</v>
       </c>
@@ -1592,7 +1624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>919</v>
       </c>
@@ -1645,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>513</v>
       </c>
@@ -1754,7 +1786,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>994</v>
       </c>
@@ -1789,7 +1821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>491</v>
       </c>
@@ -1880,7 +1912,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>705</v>
       </c>
@@ -1915,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>987</v>
       </c>
@@ -1968,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>501</v>
       </c>
@@ -2003,7 +2035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>675</v>
       </c>
@@ -2038,7 +2070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>442</v>
       </c>
@@ -2091,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>932</v>
       </c>
@@ -2126,7 +2158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>439</v>
       </c>
@@ -2179,7 +2211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>372</v>
       </c>
@@ -2232,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>710</v>
       </c>
@@ -2285,7 +2317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>375</v>
       </c>
@@ -2376,7 +2408,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>488</v>
       </c>
@@ -2429,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>521</v>
       </c>
@@ -2485,7 +2517,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>825</v>
       </c>
@@ -2520,7 +2552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>632</v>
       </c>
@@ -2607,8 +2639,11 @@
       <c r="Q29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>315</v>
       </c>
@@ -2664,7 +2699,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>449</v>
       </c>
@@ -2717,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>432</v>
       </c>
@@ -2770,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1010</v>
       </c>
@@ -2931,8 +2966,11 @@
       <c r="Q35" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>447</v>
       </c>
@@ -2988,7 +3026,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>389</v>
       </c>
@@ -3044,7 +3082,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>856</v>
       </c>
@@ -3128,7 +3166,7 @@
       <c r="J39">
         <v>7</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="3">
         <v>11.345000000000001</v>
       </c>
       <c r="L39">
@@ -3149,16 +3187,16 @@
       <c r="Q39" t="b">
         <v>0</v>
       </c>
-      <c r="R39" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R39" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>329</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C40">
         <v>5.5</v>
@@ -3258,8 +3296,8 @@
       <c r="Q41" t="b">
         <v>0</v>
       </c>
-      <c r="R41" t="s">
-        <v>74</v>
+      <c r="R41" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -3267,7 +3305,7 @@
         <v>500</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42">
         <v>4.5</v>
@@ -3314,8 +3352,11 @@
       <c r="Q42" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R42" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>670</v>
       </c>
@@ -3373,7 +3414,7 @@
         <v>711</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C44">
         <v>5.5</v>
@@ -3419,6 +3460,9 @@
       </c>
       <c r="Q44" t="b">
         <v>0</v>
+      </c>
+      <c r="R44" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -3426,7 +3470,7 @@
         <v>421</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C45">
         <v>4.5</v>
@@ -3473,16 +3517,16 @@
       <c r="Q45" t="b">
         <v>0</v>
       </c>
-      <c r="R45" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R45" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>316</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C46">
         <v>3.5</v>
@@ -3530,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -3585,11 +3629,11 @@
       <c r="Q47" t="b">
         <v>0</v>
       </c>
-      <c r="R47" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R47" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>492</v>
       </c>
@@ -3642,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>834</v>
       </c>
@@ -3677,12 +3721,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>392</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>3.5</v>
@@ -3730,15 +3774,15 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>799</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C51">
         <v>3.5</v>
@@ -3786,12 +3830,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>443</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52">
         <v>3.5</v>
@@ -3800,7 +3844,7 @@
         <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F52">
         <v>134099</v>
@@ -3839,12 +3883,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>345</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C53">
         <v>3.5</v>
@@ -3853,7 +3897,7 @@
         <v>34</v>
       </c>
       <c r="E53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F53">
         <v>136591.4</v>
@@ -3892,10 +3936,10 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>518</v>
       </c>
@@ -3948,15 +3992,15 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>269</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C55">
         <v>4.5</v>
@@ -4004,12 +4048,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>418</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C56">
         <v>7.5</v>
@@ -4057,12 +4101,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>611</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C57">
         <v>5.5</v>
@@ -4110,12 +4154,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>445</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C58">
         <v>1.5</v>
@@ -4163,12 +4207,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>735</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59">
         <v>0.5</v>
@@ -4216,12 +4260,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>692</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C60">
         <v>3.5</v>
@@ -4269,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>716</v>
       </c>
@@ -4356,13 +4400,16 @@
       <c r="Q62" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>713</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C63">
         <v>2.5</v>
@@ -4392,12 +4439,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>558</v>
       </c>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C64">
         <v>4.5</v>
@@ -4497,13 +4544,16 @@
       <c r="Q65" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>317</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66">
         <v>4.5</v>
@@ -4529,7 +4579,7 @@
       <c r="J66">
         <v>7</v>
       </c>
-      <c r="K66">
+      <c r="K66" s="1">
         <v>9.42</v>
       </c>
       <c r="L66">
@@ -4551,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="R66" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>299</v>
       </c>
@@ -4589,7 +4639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>381</v>
       </c>
@@ -4629,7 +4679,7 @@
         <v>1014</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C69">
         <v>1.5</v>
@@ -4677,15 +4727,15 @@
         <v>0</v>
       </c>
       <c r="R69" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>824</v>
       </c>
       <c r="B70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C70">
         <v>2.5</v>
@@ -4733,12 +4783,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>803</v>
       </c>
       <c r="B71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C71">
         <v>4.5</v>
@@ -4786,12 +4836,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>658</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C72">
         <v>5.5</v>
@@ -4839,12 +4889,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>318</v>
       </c>
       <c r="B73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C73">
         <v>3.5</v>
@@ -4897,7 +4947,7 @@
         <v>321</v>
       </c>
       <c r="B74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C74">
         <v>3.5</v>
@@ -4923,7 +4973,7 @@
       <c r="J74">
         <v>5</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="1">
         <v>6.5739999999999998</v>
       </c>
       <c r="L74">
@@ -4944,8 +4994,8 @@
       <c r="Q74" t="b">
         <v>0</v>
       </c>
-      <c r="R74" t="s">
-        <v>105</v>
+      <c r="R74" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -4953,7 +5003,7 @@
         <v>903</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C75">
         <v>1.5</v>
@@ -5000,13 +5050,16 @@
       <c r="Q75" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R75" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>252</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C76">
         <v>4.5</v>
@@ -5054,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>621</v>
       </c>
@@ -5107,12 +5160,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>339</v>
       </c>
       <c r="B78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>2.5</v>
@@ -5160,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>376</v>
       </c>
@@ -5213,12 +5266,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>506</v>
       </c>
       <c r="B80" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C80">
         <v>2.5</v>
@@ -5266,12 +5319,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>408</v>
       </c>
       <c r="B81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C81">
         <v>3.5</v>
@@ -5319,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>484</v>
       </c>
@@ -5372,12 +5425,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>258</v>
       </c>
       <c r="B83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C83">
         <v>3.5</v>
@@ -5386,7 +5439,7 @@
         <v>34</v>
       </c>
       <c r="E83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F83">
         <v>139544.29999999999</v>
@@ -5425,12 +5478,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>489</v>
       </c>
       <c r="B84" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C84">
         <v>2.5</v>
@@ -5478,7 +5531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>402</v>
       </c>
@@ -5531,12 +5584,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>209</v>
       </c>
       <c r="B86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>5.5</v>
@@ -5545,7 +5598,7 @@
         <v>34</v>
       </c>
       <c r="E86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F86">
         <v>140979.5</v>
@@ -5584,12 +5637,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>212</v>
       </c>
       <c r="B87" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>6.5</v>
@@ -5598,7 +5651,7 @@
         <v>34</v>
       </c>
       <c r="E87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F87">
         <v>140972</v>
@@ -5637,12 +5690,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>254</v>
       </c>
       <c r="B88" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>5.5</v>
@@ -5651,7 +5704,7 @@
         <v>34</v>
       </c>
       <c r="E88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F88">
         <v>139570.6</v>
@@ -5672,12 +5725,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>324</v>
       </c>
       <c r="B89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C89">
         <v>6.5</v>
@@ -5725,7 +5778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>495</v>
       </c>
@@ -5779,7 +5832,44 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R90" xr:uid="{CEE7B52F-37E9-4757-BFB2-50AE26839FFD}"/>
+  <autoFilter ref="A1:R90" xr:uid="{CEE7B52F-37E9-4757-BFB2-50AE26839FFD}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="firm"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="16">
+      <filters>
+        <filter val="FALSE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BBD24F9-1B07-4A25-85CB-104DC3EF0347}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>0.51790000000000003</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>9.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>1-SUM(A1:A2)</f>
+        <v>0.3901</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>